--- a/CPU Design/L1IsSequences.xlsx
+++ b/CPU Design/L1IsSequences.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Original" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'+Address bus'!$A$1:$AK$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'+Address bus'!$A$1:$AL$179</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -249,6 +249,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Selected desination(s)
+Read(s) from data bus</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R1" authorId="0">
       <text>
         <r>
@@ -449,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="Z1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -457,7 +482,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>Author:</t>
         </r>
@@ -466,11 +491,11 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Set Source ROM inside IS
-For writing it to RAM address bus</t>
+Set Destination RAM address latch inside IS
+For reading from data bus</t>
         </r>
       </text>
     </comment>
@@ -494,7 +519,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Set Source Ra RAM address inside IS
+Set Source opcode ROM inside IS
 For writing it to RAM address bus</t>
         </r>
       </text>
@@ -519,7 +544,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Set Source Rb RAM address inside IS
+Set Source Ra# RAM address inside IS
 For writing it to RAM address bus</t>
         </r>
       </text>
@@ -544,7 +569,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Set Source temporary 16 bit latch2 inside IS
+Set Source Rb# RAM address inside IS
 For writing it to RAM address bus</t>
         </r>
       </text>
@@ -569,7 +594,32 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Set Source ALU OUTPUT
+Set Source temporary 16 bit latch2 inside IS
+For writing it to RAM address bus</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AJ1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Set Source to AS latch inside IS.
 For writing it to RAM address bus</t>
         </r>
       </text>
@@ -1089,7 +1139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11399" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11557" uniqueCount="313">
   <si>
     <t>READ</t>
   </si>
@@ -1691,9 +1741,6 @@
     <t>SD_RAM</t>
   </si>
   <si>
-    <t>Abus = 15, ALU output on Dbus , prime RAM for read</t>
-  </si>
-  <si>
     <t>ALU Input A = SP</t>
   </si>
   <si>
@@ -1771,9 +1818,6 @@
   </si>
   <si>
     <t>Read PC off stack into PC</t>
-  </si>
-  <si>
-    <t>Abus = SP, RAM data on Dbus , prime PC for read</t>
   </si>
   <si>
     <t>PC = popped PC value</t>
@@ -2044,6 +2088,21 @@
   </si>
   <si>
     <t>SEQ NUM</t>
+  </si>
+  <si>
+    <t>AIS_LAT</t>
+  </si>
+  <si>
+    <t>ID_AL</t>
+  </si>
+  <si>
+    <t>Abus = 15, ALU output on Dbus , prime RAM and address latch for read</t>
+  </si>
+  <si>
+    <t>Address Latch and SP = ALU Output = SP--</t>
+  </si>
+  <si>
+    <t>Abus = Addres Latch = SP, RAM data on Dbus , prime PC for read</t>
   </si>
 </sst>
 </file>
@@ -2476,24 +2535,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK176"/>
+  <dimension ref="A1:AL176"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="13.69140625" customWidth="1"/>
     <col min="2" max="3" width="2.69140625" customWidth="1"/>
-    <col min="4" max="29" width="2.23046875" customWidth="1"/>
-    <col min="30" max="30" width="2.3046875" customWidth="1"/>
-    <col min="31" max="35" width="2.23046875" customWidth="1"/>
-    <col min="36" max="36" width="63.921875" customWidth="1"/>
-    <col min="37" max="37" width="72" customWidth="1"/>
+    <col min="4" max="30" width="2.23046875" customWidth="1"/>
+    <col min="31" max="31" width="2.3046875" customWidth="1"/>
+    <col min="32" max="36" width="2.23046875" customWidth="1"/>
+    <col min="37" max="37" width="63.921875" customWidth="1"/>
+    <col min="38" max="38" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="53.15">
+    <row r="1" spans="1:38" ht="53.15">
       <c r="A1" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>2</v>
@@ -2558,39 +2617,42 @@
       <c r="Y1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:38">
       <c r="A2" s="11"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2620,17 +2682,18 @@
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
-      <c r="AE2" s="2"/>
+      <c r="AD2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38">
       <c r="A3" s="1" t="s">
         <v>165</v>
       </c>
@@ -2698,8 +2761,8 @@
       <c r="Y3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA3" t="s">
-        <v>22</v>
+      <c r="Z3" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB3" t="s">
         <v>22</v>
@@ -2707,8 +2770,8 @@
       <c r="AC3" t="s">
         <v>22</v>
       </c>
-      <c r="AE3" s="5" t="s">
-        <v>21</v>
+      <c r="AD3" t="s">
+        <v>22</v>
       </c>
       <c r="AF3" s="5" t="s">
         <v>21</v>
@@ -2722,18 +2785,23 @@
       <c r="AI3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK3" t="s">
         <v>55</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:38">
       <c r="A4" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
       <c r="C4">
         <v>1</v>
       </c>
@@ -2794,8 +2862,8 @@
       <c r="Y4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" t="s">
-        <v>22</v>
+      <c r="Z4" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB4" t="s">
         <v>22</v>
@@ -2803,8 +2871,8 @@
       <c r="AC4" t="s">
         <v>22</v>
       </c>
-      <c r="AE4" s="5" t="s">
-        <v>21</v>
+      <c r="AD4" t="s">
+        <v>22</v>
       </c>
       <c r="AF4" s="5" t="s">
         <v>21</v>
@@ -2818,12 +2886,17 @@
       <c r="AI4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
-      <c r="B5" s="6"/>
+    <row r="5" spans="1:38">
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
       <c r="C5">
         <v>2</v>
       </c>
@@ -2884,8 +2957,8 @@
       <c r="Y5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA5" t="s">
-        <v>22</v>
+      <c r="Z5" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB5" t="s">
         <v>22</v>
@@ -2893,8 +2966,8 @@
       <c r="AC5" t="s">
         <v>22</v>
       </c>
-      <c r="AE5" s="5" t="s">
-        <v>21</v>
+      <c r="AD5" t="s">
+        <v>22</v>
       </c>
       <c r="AF5" s="5" t="s">
         <v>21</v>
@@ -2908,12 +2981,17 @@
       <c r="AI5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AJ5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
-      <c r="B6" s="6"/>
+    <row r="6" spans="1:38">
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
       <c r="C6">
         <v>3</v>
       </c>
@@ -2974,8 +3052,8 @@
       <c r="Y6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA6" t="s">
-        <v>22</v>
+      <c r="Z6" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB6" t="s">
         <v>22</v>
@@ -2983,8 +3061,8 @@
       <c r="AC6" t="s">
         <v>22</v>
       </c>
-      <c r="AE6" s="5" t="s">
-        <v>21</v>
+      <c r="AD6" t="s">
+        <v>22</v>
       </c>
       <c r="AF6" s="5" t="s">
         <v>21</v>
@@ -2998,12 +3076,17 @@
       <c r="AI6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ6" s="1" t="s">
+      <c r="AJ6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK6" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
-      <c r="B7" s="6"/>
+    <row r="7" spans="1:38">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
       <c r="C7">
         <v>4</v>
       </c>
@@ -3064,8 +3147,8 @@
       <c r="Y7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA7" t="s">
-        <v>22</v>
+      <c r="Z7" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB7" t="s">
         <v>22</v>
@@ -3073,8 +3156,8 @@
       <c r="AC7" t="s">
         <v>22</v>
       </c>
-      <c r="AE7" s="5" t="s">
-        <v>21</v>
+      <c r="AD7" t="s">
+        <v>22</v>
       </c>
       <c r="AF7" s="5" t="s">
         <v>21</v>
@@ -3088,14 +3171,17 @@
       <c r="AI7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AJ7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="s">
         <v>177</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AL7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:38">
       <c r="A9" s="1" t="s">
         <v>167</v>
       </c>
@@ -3162,8 +3248,8 @@
       <c r="Y9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA9" t="s">
-        <v>22</v>
+      <c r="Z9" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB9" t="s">
         <v>22</v>
@@ -3171,8 +3257,8 @@
       <c r="AC9" t="s">
         <v>22</v>
       </c>
-      <c r="AE9" s="5" t="s">
-        <v>21</v>
+      <c r="AD9" t="s">
+        <v>22</v>
       </c>
       <c r="AF9" s="5" t="s">
         <v>21</v>
@@ -3186,18 +3272,23 @@
       <c r="AI9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AJ9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="s">
         <v>55</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AL9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:38">
       <c r="A10" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
       <c r="C10">
         <v>1</v>
       </c>
@@ -3258,8 +3349,8 @@
       <c r="Y10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA10" t="s">
-        <v>22</v>
+      <c r="Z10" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB10" t="s">
         <v>22</v>
@@ -3267,8 +3358,8 @@
       <c r="AC10" t="s">
         <v>22</v>
       </c>
-      <c r="AE10" s="5" t="s">
-        <v>21</v>
+      <c r="AD10" t="s">
+        <v>22</v>
       </c>
       <c r="AF10" s="5" t="s">
         <v>21</v>
@@ -3282,12 +3373,17 @@
       <c r="AI10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AJ10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
-      <c r="B11" s="6"/>
+    <row r="11" spans="1:38">
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
       <c r="C11">
         <v>2</v>
       </c>
@@ -3348,8 +3444,8 @@
       <c r="Y11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA11" t="s">
-        <v>22</v>
+      <c r="Z11" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB11" t="s">
         <v>22</v>
@@ -3357,8 +3453,8 @@
       <c r="AC11" t="s">
         <v>22</v>
       </c>
-      <c r="AE11" s="5" t="s">
-        <v>21</v>
+      <c r="AD11" t="s">
+        <v>22</v>
       </c>
       <c r="AF11" s="5" t="s">
         <v>21</v>
@@ -3372,14 +3468,17 @@
       <c r="AI11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AJ11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="s">
         <v>28</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AL11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:38">
       <c r="A13" s="1" t="s">
         <v>163</v>
       </c>
@@ -3446,8 +3545,8 @@
       <c r="Y13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA13" t="s">
-        <v>22</v>
+      <c r="Z13" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB13" t="s">
         <v>22</v>
@@ -3455,8 +3554,8 @@
       <c r="AC13" t="s">
         <v>22</v>
       </c>
-      <c r="AE13" s="5" t="s">
-        <v>21</v>
+      <c r="AD13" t="s">
+        <v>22</v>
       </c>
       <c r="AF13" s="5" t="s">
         <v>21</v>
@@ -3470,15 +3569,20 @@
       <c r="AI13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AJ13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:38">
       <c r="A14" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
       <c r="C14">
         <v>1</v>
       </c>
@@ -3539,8 +3643,8 @@
       <c r="Y14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA14" s="4" t="s">
-        <v>36</v>
+      <c r="Z14" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB14" s="4" t="s">
         <v>36</v>
@@ -3548,14 +3652,14 @@
       <c r="AC14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG14" s="5" t="s">
-        <v>21</v>
+      <c r="AD14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH14" s="5" t="s">
         <v>21</v>
@@ -3563,15 +3667,20 @@
       <c r="AI14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ14" s="10" t="s">
+      <c r="AJ14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK14" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:38">
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
       <c r="C15">
         <v>2</v>
       </c>
@@ -3632,8 +3741,8 @@
       <c r="Y15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA15" s="4" t="s">
-        <v>36</v>
+      <c r="Z15" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB15" s="4" t="s">
         <v>36</v>
@@ -3641,14 +3750,14 @@
       <c r="AC15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>21</v>
+      <c r="AD15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG15" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH15" s="5" t="s">
         <v>21</v>
@@ -3656,15 +3765,20 @@
       <c r="AI15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ15" s="1" t="s">
+      <c r="AJ15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK15" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:38">
       <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
       <c r="C16">
         <v>3</v>
       </c>
@@ -3725,8 +3839,8 @@
       <c r="Y16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA16" s="4" t="s">
-        <v>36</v>
+      <c r="Z16" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB16" s="4" t="s">
         <v>36</v>
@@ -3734,8 +3848,8 @@
       <c r="AC16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE16" s="5" t="s">
-        <v>21</v>
+      <c r="AD16" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF16" s="5" t="s">
         <v>21</v>
@@ -3749,15 +3863,20 @@
       <c r="AI16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ16" t="s">
+      <c r="AJ16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:37">
+    <row r="17" spans="1:38">
       <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
       <c r="C17">
         <v>4</v>
       </c>
@@ -3818,8 +3937,8 @@
       <c r="Y17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA17" s="4" t="s">
-        <v>36</v>
+      <c r="Z17" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB17" s="4" t="s">
         <v>36</v>
@@ -3827,30 +3946,35 @@
       <c r="AC17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE17" s="5" t="s">
-        <v>21</v>
+      <c r="AD17" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH17" s="5" t="s">
-        <v>21</v>
+      <c r="AG17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH17" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ17" s="10" t="s">
+      <c r="AJ17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK17" s="10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:37">
+    <row r="18" spans="1:38">
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
       <c r="C18">
         <v>5</v>
       </c>
@@ -3911,8 +4035,8 @@
       <c r="Y18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA18" s="4" t="s">
-        <v>36</v>
+      <c r="Z18" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB18" s="4" t="s">
         <v>36</v>
@@ -3920,30 +4044,35 @@
       <c r="AC18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE18" s="5" t="s">
-        <v>21</v>
+      <c r="AD18" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH18" s="5" t="s">
-        <v>21</v>
+      <c r="AG18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH18" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ18" s="1" t="s">
+      <c r="AJ18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK18" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:37">
+    <row r="19" spans="1:38">
       <c r="A19" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
       <c r="C19">
         <v>6</v>
       </c>
@@ -4004,8 +4133,8 @@
       <c r="Y19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA19" s="4" t="s">
-        <v>36</v>
+      <c r="Z19" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB19" s="4" t="s">
         <v>36</v>
@@ -4013,8 +4142,8 @@
       <c r="AC19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE19" s="5" t="s">
-        <v>21</v>
+      <c r="AD19" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF19" s="5" t="s">
         <v>21</v>
@@ -4028,12 +4157,17 @@
       <c r="AI19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ19" t="s">
+      <c r="AJ19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
-      <c r="B20" s="6"/>
+    <row r="20" spans="1:38">
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
       <c r="C20">
         <v>7</v>
       </c>
@@ -4094,8 +4228,8 @@
       <c r="Y20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA20" s="4" t="s">
-        <v>36</v>
+      <c r="Z20" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB20" s="4" t="s">
         <v>36</v>
@@ -4103,14 +4237,14 @@
       <c r="AC20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG20" s="5" t="s">
-        <v>21</v>
+      <c r="AD20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH20" s="5" t="s">
         <v>21</v>
@@ -4118,12 +4252,17 @@
       <c r="AI20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ20" s="10" t="s">
+      <c r="AJ20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK20" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="1:37">
-      <c r="B21" s="6"/>
+    <row r="21" spans="1:38">
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
       <c r="C21">
         <v>8</v>
       </c>
@@ -4184,8 +4323,8 @@
       <c r="Y21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA21" s="4" t="s">
-        <v>36</v>
+      <c r="Z21" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB21" s="4" t="s">
         <v>36</v>
@@ -4193,14 +4332,14 @@
       <c r="AC21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG21" s="5" t="s">
-        <v>21</v>
+      <c r="AD21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG21" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH21" s="5" t="s">
         <v>21</v>
@@ -4208,12 +4347,17 @@
       <c r="AI21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ21" s="1" t="s">
+      <c r="AJ21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK21" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:37">
-      <c r="B22" s="6"/>
+    <row r="22" spans="1:38">
+      <c r="B22" s="1">
+        <v>2</v>
+      </c>
       <c r="C22">
         <v>9</v>
       </c>
@@ -4274,8 +4418,8 @@
       <c r="Y22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA22" s="4" t="s">
-        <v>36</v>
+      <c r="Z22" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB22" s="4" t="s">
         <v>36</v>
@@ -4283,8 +4427,8 @@
       <c r="AC22" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE22" s="5" t="s">
-        <v>21</v>
+      <c r="AD22" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>21</v>
@@ -4298,14 +4442,17 @@
       <c r="AI22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ22" t="s">
+      <c r="AJ22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="s">
         <v>45</v>
       </c>
-      <c r="AK22" t="s">
+      <c r="AL22" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:37">
+    <row r="24" spans="1:38">
       <c r="A24" s="1" t="s">
         <v>169</v>
       </c>
@@ -4372,8 +4519,8 @@
       <c r="Y24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA24" t="s">
-        <v>22</v>
+      <c r="Z24" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB24" t="s">
         <v>22</v>
@@ -4381,8 +4528,8 @@
       <c r="AC24" t="s">
         <v>22</v>
       </c>
-      <c r="AE24" s="5" t="s">
-        <v>21</v>
+      <c r="AD24" t="s">
+        <v>22</v>
       </c>
       <c r="AF24" s="5" t="s">
         <v>21</v>
@@ -4396,14 +4543,20 @@
       <c r="AI24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ24" t="s">
+      <c r="AJ24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
+    <row r="25" spans="1:38">
       <c r="A25" s="1" t="s">
         <v>170</v>
       </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
       <c r="C25">
         <v>1</v>
       </c>
@@ -4464,8 +4617,8 @@
       <c r="Y25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA25" s="4" t="s">
-        <v>36</v>
+      <c r="Z25" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB25" s="4" t="s">
         <v>36</v>
@@ -4473,14 +4626,14 @@
       <c r="AC25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG25" s="5" t="s">
-        <v>21</v>
+      <c r="AD25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG25" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH25" s="5" t="s">
         <v>21</v>
@@ -4488,14 +4641,20 @@
       <c r="AI25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ25" s="10" t="s">
+      <c r="AJ25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK25" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:38">
       <c r="A26" t="s">
         <v>48</v>
       </c>
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
       <c r="C26">
         <v>2</v>
       </c>
@@ -4556,8 +4715,8 @@
       <c r="Y26" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA26" s="4" t="s">
-        <v>36</v>
+      <c r="Z26" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB26" s="4" t="s">
         <v>36</v>
@@ -4565,14 +4724,14 @@
       <c r="AC26" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF26" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG26" s="5" t="s">
-        <v>21</v>
+      <c r="AD26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG26" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH26" s="5" t="s">
         <v>21</v>
@@ -4580,11 +4739,17 @@
       <c r="AI26" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ26" s="1" t="s">
+      <c r="AJ26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK26" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:38">
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
       <c r="C27">
         <v>3</v>
       </c>
@@ -4645,8 +4810,8 @@
       <c r="Y27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA27" s="4" t="s">
-        <v>36</v>
+      <c r="Z27" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB27" s="4" t="s">
         <v>36</v>
@@ -4654,8 +4819,8 @@
       <c r="AC27" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE27" s="5" t="s">
-        <v>21</v>
+      <c r="AD27" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF27" s="5" t="s">
         <v>21</v>
@@ -4669,11 +4834,17 @@
       <c r="AI27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ27" t="s">
+      <c r="AJ27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:37">
+    <row r="28" spans="1:38">
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
       <c r="C28">
         <v>4</v>
       </c>
@@ -4734,8 +4905,8 @@
       <c r="Y28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA28" s="4" t="s">
-        <v>36</v>
+      <c r="Z28" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB28" s="4" t="s">
         <v>36</v>
@@ -4743,14 +4914,14 @@
       <c r="AC28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE28" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG28" s="5" t="s">
-        <v>21</v>
+      <c r="AD28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG28" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH28" s="5" t="s">
         <v>21</v>
@@ -4758,11 +4929,17 @@
       <c r="AI28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ28" s="10" t="s">
+      <c r="AJ28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK28" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:38">
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
       <c r="C29">
         <v>5</v>
       </c>
@@ -4823,8 +5000,8 @@
       <c r="Y29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA29" s="4" t="s">
-        <v>36</v>
+      <c r="Z29" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB29" s="4" t="s">
         <v>36</v>
@@ -4832,14 +5009,14 @@
       <c r="AC29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE29" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG29" s="5" t="s">
-        <v>21</v>
+      <c r="AD29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG29" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH29" s="5" t="s">
         <v>21</v>
@@ -4847,11 +5024,17 @@
       <c r="AI29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ29" s="1" t="s">
+      <c r="AJ29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK29" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:38">
+      <c r="B30" s="1">
+        <v>3</v>
+      </c>
       <c r="C30">
         <v>6</v>
       </c>
@@ -4912,8 +5095,8 @@
       <c r="Y30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA30" s="4" t="s">
-        <v>36</v>
+      <c r="Z30" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB30" s="4" t="s">
         <v>36</v>
@@ -4921,8 +5104,8 @@
       <c r="AC30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE30" s="5" t="s">
-        <v>21</v>
+      <c r="AD30" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="AF30" s="5" t="s">
         <v>21</v>
@@ -4936,14 +5119,17 @@
       <c r="AI30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ30" t="s">
+      <c r="AJ30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK30" t="s">
         <v>45</v>
       </c>
-      <c r="AK30" t="s">
+      <c r="AL30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:37">
+    <row r="32" spans="1:38">
       <c r="A32" s="1" t="s">
         <v>49</v>
       </c>
@@ -5010,8 +5196,8 @@
       <c r="Y32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA32" t="s">
-        <v>22</v>
+      <c r="Z32" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB32" t="s">
         <v>22</v>
@@ -5019,8 +5205,8 @@
       <c r="AC32" t="s">
         <v>22</v>
       </c>
-      <c r="AE32" s="5" t="s">
-        <v>21</v>
+      <c r="AD32" t="s">
+        <v>22</v>
       </c>
       <c r="AF32" s="5" t="s">
         <v>21</v>
@@ -5034,11 +5220,17 @@
       <c r="AI32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ32" t="s">
+      <c r="AJ32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK32" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:38">
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
       <c r="C33">
         <v>1</v>
       </c>
@@ -5099,8 +5291,8 @@
       <c r="Y33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA33" t="s">
-        <v>22</v>
+      <c r="Z33" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB33" t="s">
         <v>22</v>
@@ -5108,26 +5300,32 @@
       <c r="AC33" t="s">
         <v>22</v>
       </c>
-      <c r="AE33" s="5" t="s">
-        <v>21</v>
+      <c r="AD33" t="s">
+        <v>22</v>
       </c>
       <c r="AF33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH33" s="5" t="s">
-        <v>21</v>
+      <c r="AG33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH33" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ33" s="10" t="s">
+      <c r="AJ33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK33" s="10" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:37">
+    <row r="34" spans="1:38">
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
       <c r="C34">
         <v>2</v>
       </c>
@@ -5188,8 +5386,8 @@
       <c r="Y34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA34" t="s">
-        <v>22</v>
+      <c r="Z34" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB34" t="s">
         <v>22</v>
@@ -5197,26 +5395,32 @@
       <c r="AC34" t="s">
         <v>22</v>
       </c>
-      <c r="AE34" s="5" t="s">
-        <v>21</v>
+      <c r="AD34" t="s">
+        <v>22</v>
       </c>
       <c r="AF34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH34" s="5" t="s">
-        <v>21</v>
+      <c r="AG34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH34" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI34" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ34" s="1" t="s">
+      <c r="AJ34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK34" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:37">
+    <row r="35" spans="1:38">
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
       <c r="C35">
         <v>3</v>
       </c>
@@ -5277,8 +5481,8 @@
       <c r="Y35" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA35" t="s">
-        <v>22</v>
+      <c r="Z35" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB35" t="s">
         <v>22</v>
@@ -5286,8 +5490,8 @@
       <c r="AC35" t="s">
         <v>22</v>
       </c>
-      <c r="AE35" s="5" t="s">
-        <v>21</v>
+      <c r="AD35" t="s">
+        <v>22</v>
       </c>
       <c r="AF35" s="5" t="s">
         <v>21</v>
@@ -5301,11 +5505,17 @@
       <c r="AI35" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ35" t="s">
+      <c r="AJ35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK35" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:37">
+    <row r="36" spans="1:38">
+      <c r="B36" s="1">
+        <v>4</v>
+      </c>
       <c r="C36">
         <v>4</v>
       </c>
@@ -5366,8 +5576,8 @@
       <c r="Y36" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA36" t="s">
-        <v>22</v>
+      <c r="Z36" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB36" t="s">
         <v>22</v>
@@ -5375,14 +5585,14 @@
       <c r="AC36" t="s">
         <v>22</v>
       </c>
-      <c r="AE36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF36" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG36" s="5" t="s">
-        <v>21</v>
+      <c r="AD36" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG36" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH36" s="5" t="s">
         <v>21</v>
@@ -5390,11 +5600,17 @@
       <c r="AI36" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ36" s="10" t="s">
+      <c r="AJ36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK36" s="10" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:37">
+    <row r="37" spans="1:38">
+      <c r="B37" s="1">
+        <v>4</v>
+      </c>
       <c r="C37">
         <v>5</v>
       </c>
@@ -5455,8 +5671,8 @@
       <c r="Y37" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA37" t="s">
-        <v>22</v>
+      <c r="Z37" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB37" t="s">
         <v>22</v>
@@ -5464,14 +5680,14 @@
       <c r="AC37" t="s">
         <v>22</v>
       </c>
-      <c r="AE37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF37" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG37" s="5" t="s">
-        <v>21</v>
+      <c r="AD37" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG37" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH37" s="5" t="s">
         <v>21</v>
@@ -5479,11 +5695,17 @@
       <c r="AI37" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ37" s="1" t="s">
+      <c r="AJ37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK37" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="38" spans="1:37">
+    <row r="38" spans="1:38">
+      <c r="B38" s="1">
+        <v>4</v>
+      </c>
       <c r="C38">
         <v>6</v>
       </c>
@@ -5544,8 +5766,8 @@
       <c r="Y38" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA38" t="s">
-        <v>22</v>
+      <c r="Z38" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB38" t="s">
         <v>22</v>
@@ -5553,8 +5775,8 @@
       <c r="AC38" t="s">
         <v>22</v>
       </c>
-      <c r="AE38" s="5" t="s">
-        <v>21</v>
+      <c r="AD38" t="s">
+        <v>22</v>
       </c>
       <c r="AF38" s="5" t="s">
         <v>21</v>
@@ -5568,14 +5790,17 @@
       <c r="AI38" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ38" t="s">
+      <c r="AJ38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK38" t="s">
         <v>45</v>
       </c>
-      <c r="AK38" t="s">
+      <c r="AL38" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:37">
+    <row r="40" spans="1:38">
       <c r="A40" s="1" t="s">
         <v>54</v>
       </c>
@@ -5642,8 +5867,8 @@
       <c r="Y40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA40" t="s">
-        <v>22</v>
+      <c r="Z40" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB40" t="s">
         <v>22</v>
@@ -5651,8 +5876,8 @@
       <c r="AC40" t="s">
         <v>22</v>
       </c>
-      <c r="AE40" s="5" t="s">
-        <v>21</v>
+      <c r="AD40" t="s">
+        <v>22</v>
       </c>
       <c r="AF40" s="5" t="s">
         <v>21</v>
@@ -5666,11 +5891,17 @@
       <c r="AI40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ40" t="s">
+      <c r="AJ40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK40" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:37">
+    <row r="41" spans="1:38">
+      <c r="B41" s="1">
+        <v>5</v>
+      </c>
       <c r="C41">
         <v>1</v>
       </c>
@@ -5731,8 +5962,8 @@
       <c r="Y41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA41" t="s">
-        <v>22</v>
+      <c r="Z41" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB41" t="s">
         <v>22</v>
@@ -5740,11 +5971,11 @@
       <c r="AC41" t="s">
         <v>22</v>
       </c>
-      <c r="AE41" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF41" s="5" t="s">
-        <v>21</v>
+      <c r="AD41" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF41" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG41" s="5" t="s">
         <v>21</v>
@@ -5755,11 +5986,17 @@
       <c r="AI41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ41" s="10" t="s">
+      <c r="AJ41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK41" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="42" spans="1:37">
+    <row r="42" spans="1:38">
+      <c r="B42" s="1">
+        <v>5</v>
+      </c>
       <c r="C42">
         <v>2</v>
       </c>
@@ -5820,8 +6057,8 @@
       <c r="Y42" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA42" t="s">
-        <v>22</v>
+      <c r="Z42" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB42" t="s">
         <v>22</v>
@@ -5829,11 +6066,11 @@
       <c r="AC42" t="s">
         <v>22</v>
       </c>
-      <c r="AE42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF42" s="5" t="s">
-        <v>21</v>
+      <c r="AD42" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF42" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG42" s="5" t="s">
         <v>21</v>
@@ -5844,11 +6081,17 @@
       <c r="AI42" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ42" s="1" t="s">
+      <c r="AJ42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK42" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="43" spans="1:37">
+    <row r="43" spans="1:38">
+      <c r="B43" s="1">
+        <v>5</v>
+      </c>
       <c r="C43">
         <v>3</v>
       </c>
@@ -5909,8 +6152,8 @@
       <c r="Y43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA43" t="s">
-        <v>22</v>
+      <c r="Z43" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB43" t="s">
         <v>22</v>
@@ -5918,8 +6161,8 @@
       <c r="AC43" t="s">
         <v>22</v>
       </c>
-      <c r="AE43" s="5" t="s">
-        <v>21</v>
+      <c r="AD43" t="s">
+        <v>22</v>
       </c>
       <c r="AF43" s="5" t="s">
         <v>21</v>
@@ -5933,14 +6176,17 @@
       <c r="AI43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ43" t="s">
+      <c r="AJ43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK43" t="s">
         <v>45</v>
       </c>
-      <c r="AK43" t="s">
+      <c r="AL43" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:37">
+    <row r="45" spans="1:38">
       <c r="A45" s="1" t="s">
         <v>59</v>
       </c>
@@ -6007,8 +6253,8 @@
       <c r="Y45" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA45" t="s">
-        <v>22</v>
+      <c r="Z45" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB45" t="s">
         <v>22</v>
@@ -6016,8 +6262,8 @@
       <c r="AC45" t="s">
         <v>22</v>
       </c>
-      <c r="AE45" s="5" t="s">
-        <v>21</v>
+      <c r="AD45" t="s">
+        <v>22</v>
       </c>
       <c r="AF45" s="5" t="s">
         <v>21</v>
@@ -6031,11 +6277,17 @@
       <c r="AI45" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ45" t="s">
+      <c r="AJ45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK45" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:37">
+    <row r="46" spans="1:38">
+      <c r="B46" s="1">
+        <v>6</v>
+      </c>
       <c r="C46">
         <v>1</v>
       </c>
@@ -6096,8 +6348,8 @@
       <c r="Y46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA46" s="4" t="s">
-        <v>60</v>
+      <c r="Z46" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB46" s="4" t="s">
         <v>60</v>
@@ -6105,14 +6357,14 @@
       <c r="AC46" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE46" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF46" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG46" s="5" t="s">
-        <v>21</v>
+      <c r="AD46" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG46" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH46" s="5" t="s">
         <v>21</v>
@@ -6120,11 +6372,17 @@
       <c r="AI46" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ46" s="10" t="s">
+      <c r="AJ46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK46" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:37">
+    <row r="47" spans="1:38">
+      <c r="B47" s="1">
+        <v>6</v>
+      </c>
       <c r="C47">
         <v>2</v>
       </c>
@@ -6185,8 +6443,8 @@
       <c r="Y47" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA47" s="4" t="s">
-        <v>60</v>
+      <c r="Z47" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB47" s="4" t="s">
         <v>60</v>
@@ -6194,14 +6452,14 @@
       <c r="AC47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE47" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF47" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG47" s="5" t="s">
-        <v>21</v>
+      <c r="AD47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG47" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH47" s="5" t="s">
         <v>21</v>
@@ -6209,11 +6467,17 @@
       <c r="AI47" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ47" s="1" t="s">
+      <c r="AJ47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK47" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="1:37">
+    <row r="48" spans="1:38">
+      <c r="B48" s="1">
+        <v>6</v>
+      </c>
       <c r="C48">
         <v>3</v>
       </c>
@@ -6274,8 +6538,8 @@
       <c r="Y48" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA48" s="4" t="s">
-        <v>60</v>
+      <c r="Z48" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB48" s="4" t="s">
         <v>60</v>
@@ -6283,8 +6547,8 @@
       <c r="AC48" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE48" s="5" t="s">
-        <v>21</v>
+      <c r="AD48" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF48" s="5" t="s">
         <v>21</v>
@@ -6298,11 +6562,17 @@
       <c r="AI48" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ48" t="s">
+      <c r="AJ48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK48" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:37">
+    <row r="49" spans="1:38">
+      <c r="B49" s="1">
+        <v>6</v>
+      </c>
       <c r="C49">
         <v>4</v>
       </c>
@@ -6363,8 +6633,8 @@
       <c r="Y49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA49" s="4" t="s">
-        <v>60</v>
+      <c r="Z49" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB49" s="4" t="s">
         <v>60</v>
@@ -6372,8 +6642,8 @@
       <c r="AC49" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE49" s="5" t="s">
-        <v>21</v>
+      <c r="AD49" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF49" s="5" t="s">
         <v>21</v>
@@ -6387,11 +6657,17 @@
       <c r="AI49" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ49" t="s">
+      <c r="AJ49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK49" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:37">
+    <row r="50" spans="1:38">
+      <c r="B50" s="1">
+        <v>6</v>
+      </c>
       <c r="C50">
         <v>5</v>
       </c>
@@ -6452,8 +6728,8 @@
       <c r="Y50" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA50" s="4" t="s">
-        <v>60</v>
+      <c r="Z50" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB50" s="4" t="s">
         <v>60</v>
@@ -6461,8 +6737,8 @@
       <c r="AC50" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE50" s="5" t="s">
-        <v>21</v>
+      <c r="AD50" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF50" s="5" t="s">
         <v>21</v>
@@ -6476,11 +6752,17 @@
       <c r="AI50" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ50" s="1" t="s">
+      <c r="AJ50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK50" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:37">
+    <row r="51" spans="1:38">
+      <c r="B51" s="1">
+        <v>6</v>
+      </c>
       <c r="C51">
         <v>6</v>
       </c>
@@ -6541,8 +6823,8 @@
       <c r="Y51" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA51" s="4" t="s">
-        <v>60</v>
+      <c r="Z51" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB51" s="4" t="s">
         <v>60</v>
@@ -6550,8 +6832,8 @@
       <c r="AC51" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE51" s="5" t="s">
-        <v>21</v>
+      <c r="AD51" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF51" s="5" t="s">
         <v>21</v>
@@ -6565,11 +6847,17 @@
       <c r="AI51" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ51" t="s">
+      <c r="AJ51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK51" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:37">
+    <row r="52" spans="1:38">
+      <c r="B52" s="1">
+        <v>6</v>
+      </c>
       <c r="C52">
         <v>7</v>
       </c>
@@ -6630,8 +6918,8 @@
       <c r="Y52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA52" s="4" t="s">
-        <v>60</v>
+      <c r="Z52" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB52" s="4" t="s">
         <v>60</v>
@@ -6639,14 +6927,14 @@
       <c r="AC52" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG52" s="5" t="s">
-        <v>21</v>
+      <c r="AD52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG52" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH52" s="5" t="s">
         <v>21</v>
@@ -6654,11 +6942,17 @@
       <c r="AI52" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ52" s="10" t="s">
+      <c r="AJ52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK52" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="1:37">
+    <row r="53" spans="1:38">
+      <c r="B53" s="1">
+        <v>6</v>
+      </c>
       <c r="C53">
         <v>8</v>
       </c>
@@ -6719,8 +7013,8 @@
       <c r="Y53" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA53" s="4" t="s">
-        <v>60</v>
+      <c r="Z53" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB53" s="4" t="s">
         <v>60</v>
@@ -6728,14 +7022,14 @@
       <c r="AC53" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE53" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF53" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG53" s="5" t="s">
-        <v>21</v>
+      <c r="AD53" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG53" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH53" s="5" t="s">
         <v>21</v>
@@ -6743,11 +7037,17 @@
       <c r="AI53" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ53" s="1" t="s">
+      <c r="AJ53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK53" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:37">
+    <row r="54" spans="1:38">
+      <c r="B54" s="1">
+        <v>6</v>
+      </c>
       <c r="C54">
         <v>9</v>
       </c>
@@ -6808,8 +7108,8 @@
       <c r="Y54" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA54" s="4" t="s">
-        <v>60</v>
+      <c r="Z54" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB54" s="4" t="s">
         <v>60</v>
@@ -6817,8 +7117,8 @@
       <c r="AC54" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE54" s="5" t="s">
-        <v>21</v>
+      <c r="AD54" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF54" s="5" t="s">
         <v>21</v>
@@ -6832,14 +7132,17 @@
       <c r="AI54" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ54" t="s">
+      <c r="AJ54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK54" t="s">
         <v>45</v>
       </c>
-      <c r="AK54" t="s">
+      <c r="AL54" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:37">
+    <row r="56" spans="1:38">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -6906,8 +7209,8 @@
       <c r="Y56" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA56" t="s">
-        <v>22</v>
+      <c r="Z56" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB56" t="s">
         <v>22</v>
@@ -6915,8 +7218,8 @@
       <c r="AC56" t="s">
         <v>22</v>
       </c>
-      <c r="AE56" s="5" t="s">
-        <v>21</v>
+      <c r="AD56" t="s">
+        <v>22</v>
       </c>
       <c r="AF56" s="5" t="s">
         <v>21</v>
@@ -6930,14 +7233,20 @@
       <c r="AI56" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ56" t="s">
+      <c r="AJ56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK56" t="s">
         <v>55</v>
       </c>
-      <c r="AK56" t="s">
+      <c r="AL56" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:37">
+    <row r="57" spans="1:38">
+      <c r="B57" s="1">
+        <v>6</v>
+      </c>
       <c r="C57">
         <v>1</v>
       </c>
@@ -6998,8 +7307,8 @@
       <c r="Y57" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA57" s="7" t="s">
-        <v>64</v>
+      <c r="Z57" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB57" s="7" t="s">
         <v>64</v>
@@ -7007,14 +7316,14 @@
       <c r="AC57" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE57" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF57" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG57" s="5" t="s">
-        <v>21</v>
+      <c r="AD57" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF57" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG57" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH57" s="5" t="s">
         <v>21</v>
@@ -7022,11 +7331,17 @@
       <c r="AI57" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ57" s="10" t="s">
+      <c r="AJ57" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK57" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="58" spans="1:37">
+    <row r="58" spans="1:38">
+      <c r="B58" s="1">
+        <v>6</v>
+      </c>
       <c r="C58">
         <v>2</v>
       </c>
@@ -7087,8 +7402,8 @@
       <c r="Y58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA58" s="7" t="s">
-        <v>64</v>
+      <c r="Z58" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB58" s="7" t="s">
         <v>64</v>
@@ -7096,14 +7411,14 @@
       <c r="AC58" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE58" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF58" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG58" s="5" t="s">
-        <v>21</v>
+      <c r="AD58" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF58" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG58" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH58" s="5" t="s">
         <v>21</v>
@@ -7111,11 +7426,17 @@
       <c r="AI58" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ58" s="1" t="s">
+      <c r="AJ58" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK58" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="59" spans="1:37">
+    <row r="59" spans="1:38">
+      <c r="B59" s="1">
+        <v>6</v>
+      </c>
       <c r="C59">
         <v>3</v>
       </c>
@@ -7176,8 +7497,8 @@
       <c r="Y59" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA59" s="7" t="s">
-        <v>64</v>
+      <c r="Z59" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB59" s="7" t="s">
         <v>64</v>
@@ -7185,8 +7506,8 @@
       <c r="AC59" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE59" s="5" t="s">
-        <v>21</v>
+      <c r="AD59" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF59" s="5" t="s">
         <v>21</v>
@@ -7200,11 +7521,17 @@
       <c r="AI59" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ59" t="s">
+      <c r="AJ59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK59" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:37">
+    <row r="60" spans="1:38">
+      <c r="B60" s="1">
+        <v>6</v>
+      </c>
       <c r="C60">
         <v>4</v>
       </c>
@@ -7265,8 +7592,8 @@
       <c r="Y60" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA60" s="7" t="s">
-        <v>64</v>
+      <c r="Z60" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB60" s="7" t="s">
         <v>64</v>
@@ -7274,8 +7601,8 @@
       <c r="AC60" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE60" s="5" t="s">
-        <v>21</v>
+      <c r="AD60" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF60" s="5" t="s">
         <v>21</v>
@@ -7289,11 +7616,17 @@
       <c r="AI60" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ60" t="s">
+      <c r="AJ60" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK60" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:37">
+    <row r="61" spans="1:38">
+      <c r="B61" s="1">
+        <v>6</v>
+      </c>
       <c r="C61">
         <v>5</v>
       </c>
@@ -7354,8 +7687,8 @@
       <c r="Y61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA61" s="7" t="s">
-        <v>64</v>
+      <c r="Z61" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB61" s="7" t="s">
         <v>64</v>
@@ -7363,8 +7696,8 @@
       <c r="AC61" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE61" s="5" t="s">
-        <v>21</v>
+      <c r="AD61" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF61" s="5" t="s">
         <v>21</v>
@@ -7378,11 +7711,17 @@
       <c r="AI61" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ61" s="1" t="s">
+      <c r="AJ61" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK61" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="1:37">
+    <row r="62" spans="1:38">
+      <c r="B62" s="1">
+        <v>6</v>
+      </c>
       <c r="C62">
         <v>6</v>
       </c>
@@ -7443,8 +7782,8 @@
       <c r="Y62" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA62" s="7" t="s">
-        <v>64</v>
+      <c r="Z62" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB62" s="7" t="s">
         <v>64</v>
@@ -7452,8 +7791,8 @@
       <c r="AC62" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE62" s="5" t="s">
-        <v>21</v>
+      <c r="AD62" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF62" s="5" t="s">
         <v>21</v>
@@ -7467,11 +7806,17 @@
       <c r="AI62" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ62" t="s">
+      <c r="AJ62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK62" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="63" spans="1:37">
+    <row r="63" spans="1:38">
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
       <c r="C63">
         <v>7</v>
       </c>
@@ -7532,8 +7877,8 @@
       <c r="Y63" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA63" s="7" t="s">
-        <v>64</v>
+      <c r="Z63" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB63" s="7" t="s">
         <v>64</v>
@@ -7541,14 +7886,14 @@
       <c r="AC63" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE63" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF63" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG63" s="5" t="s">
-        <v>21</v>
+      <c r="AD63" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF63" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG63" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH63" s="5" t="s">
         <v>21</v>
@@ -7556,11 +7901,17 @@
       <c r="AI63" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ63" s="10" t="s">
+      <c r="AJ63" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK63" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="64" spans="1:37">
+    <row r="64" spans="1:38">
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
       <c r="C64">
         <v>8</v>
       </c>
@@ -7621,8 +7972,8 @@
       <c r="Y64" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA64" s="7" t="s">
-        <v>64</v>
+      <c r="Z64" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB64" s="7" t="s">
         <v>64</v>
@@ -7630,14 +7981,14 @@
       <c r="AC64" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE64" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF64" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG64" s="5" t="s">
-        <v>21</v>
+      <c r="AD64" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF64" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG64" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH64" s="5" t="s">
         <v>21</v>
@@ -7645,11 +7996,17 @@
       <c r="AI64" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ64" s="1" t="s">
+      <c r="AJ64" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK64" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="65" spans="1:37">
+    <row r="65" spans="1:38">
+      <c r="B65" s="1">
+        <v>6</v>
+      </c>
       <c r="C65">
         <v>9</v>
       </c>
@@ -7710,8 +8067,8 @@
       <c r="Y65" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA65" s="7" t="s">
-        <v>64</v>
+      <c r="Z65" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB65" s="7" t="s">
         <v>64</v>
@@ -7719,8 +8076,8 @@
       <c r="AC65" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE65" s="5" t="s">
-        <v>21</v>
+      <c r="AD65" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF65" s="5" t="s">
         <v>21</v>
@@ -7734,14 +8091,17 @@
       <c r="AI65" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ65" t="s">
+      <c r="AJ65" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK65" t="s">
         <v>45</v>
       </c>
-      <c r="AK65" t="s">
+      <c r="AL65" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:37">
+    <row r="67" spans="1:38">
       <c r="A67" s="1" t="s">
         <v>63</v>
       </c>
@@ -7808,8 +8168,8 @@
       <c r="Y67" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA67" t="s">
-        <v>22</v>
+      <c r="Z67" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB67" t="s">
         <v>22</v>
@@ -7817,8 +8177,8 @@
       <c r="AC67" t="s">
         <v>22</v>
       </c>
-      <c r="AE67" s="5" t="s">
-        <v>21</v>
+      <c r="AD67" t="s">
+        <v>22</v>
       </c>
       <c r="AF67" s="5" t="s">
         <v>21</v>
@@ -7832,11 +8192,17 @@
       <c r="AI67" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ67" t="s">
+      <c r="AJ67" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK67" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:37">
+    <row r="68" spans="1:38">
+      <c r="B68" s="1">
+        <v>7</v>
+      </c>
       <c r="C68">
         <v>1</v>
       </c>
@@ -7897,8 +8263,8 @@
       <c r="Y68" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA68" s="7" t="s">
-        <v>64</v>
+      <c r="Z68" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB68" s="7" t="s">
         <v>64</v>
@@ -7906,29 +8272,35 @@
       <c r="AC68" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE68" s="5" t="s">
-        <v>21</v>
+      <c r="AD68" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF68" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG68" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH68" s="5" t="s">
-        <v>21</v>
+      <c r="AG68" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH68" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI68" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ68" s="10" t="s">
+      <c r="AJ68" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK68" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AK68" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="69" spans="1:37">
+      <c r="AL68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38">
+      <c r="B69" s="1">
+        <v>7</v>
+      </c>
       <c r="C69">
         <v>2</v>
       </c>
@@ -7989,8 +8361,8 @@
       <c r="Y69" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA69" s="7" t="s">
-        <v>64</v>
+      <c r="Z69" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB69" s="7" t="s">
         <v>64</v>
@@ -7998,29 +8370,35 @@
       <c r="AC69" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE69" s="5" t="s">
-        <v>21</v>
+      <c r="AD69" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF69" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG69" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH69" s="5" t="s">
-        <v>21</v>
+      <c r="AG69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH69" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI69" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ69" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK69" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="70" spans="1:37">
+      <c r="AJ69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK69" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38">
+      <c r="B70" s="1">
+        <v>7</v>
+      </c>
       <c r="C70">
         <v>3</v>
       </c>
@@ -8081,8 +8459,8 @@
       <c r="Y70" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA70" s="7" t="s">
-        <v>64</v>
+      <c r="Z70" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB70" s="7" t="s">
         <v>64</v>
@@ -8090,8 +8468,8 @@
       <c r="AC70" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE70" s="5" t="s">
-        <v>21</v>
+      <c r="AD70" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF70" s="5" t="s">
         <v>21</v>
@@ -8105,14 +8483,20 @@
       <c r="AI70" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ70" t="s">
+      <c r="AJ70" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK70" t="s">
         <v>26</v>
       </c>
-      <c r="AK70" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="71" spans="1:37">
+      <c r="AL70" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38">
+      <c r="B71" s="1">
+        <v>7</v>
+      </c>
       <c r="C71">
         <v>4</v>
       </c>
@@ -8173,8 +8557,8 @@
       <c r="Y71" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA71" s="7" t="s">
-        <v>64</v>
+      <c r="Z71" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB71" s="7" t="s">
         <v>64</v>
@@ -8182,8 +8566,8 @@
       <c r="AC71" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE71" s="5" t="s">
-        <v>21</v>
+      <c r="AD71" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF71" s="5" t="s">
         <v>21</v>
@@ -8197,14 +8581,20 @@
       <c r="AI71" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ71" t="s">
+      <c r="AJ71" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK71" t="s">
         <v>179</v>
       </c>
-      <c r="AK71" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="72" spans="1:37">
+      <c r="AL71" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38">
+      <c r="B72" s="1">
+        <v>7</v>
+      </c>
       <c r="C72">
         <v>5</v>
       </c>
@@ -8265,8 +8655,8 @@
       <c r="Y72" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA72" s="7" t="s">
-        <v>64</v>
+      <c r="Z72" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB72" s="7" t="s">
         <v>64</v>
@@ -8274,8 +8664,8 @@
       <c r="AC72" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE72" s="5" t="s">
-        <v>21</v>
+      <c r="AD72" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF72" s="5" t="s">
         <v>21</v>
@@ -8289,14 +8679,20 @@
       <c r="AI72" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ72" s="1" t="s">
+      <c r="AJ72" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK72" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AK72" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="73" spans="1:37">
+      <c r="AL72" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38">
+      <c r="B73" s="1">
+        <v>7</v>
+      </c>
       <c r="C73">
         <v>6</v>
       </c>
@@ -8357,8 +8753,8 @@
       <c r="Y73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA73" s="7" t="s">
-        <v>64</v>
+      <c r="Z73" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB73" s="7" t="s">
         <v>64</v>
@@ -8366,8 +8762,8 @@
       <c r="AC73" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE73" s="5" t="s">
-        <v>21</v>
+      <c r="AD73" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF73" s="5" t="s">
         <v>21</v>
@@ -8381,14 +8777,20 @@
       <c r="AI73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ73" t="s">
+      <c r="AJ73" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK73" t="s">
         <v>26</v>
       </c>
-      <c r="AK73" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="74" spans="1:37">
+      <c r="AL73" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="74" spans="1:38">
+      <c r="B74" s="1">
+        <v>7</v>
+      </c>
       <c r="C74">
         <v>7</v>
       </c>
@@ -8449,8 +8851,8 @@
       <c r="Y74" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA74" s="7" t="s">
-        <v>64</v>
+      <c r="Z74" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AB74" s="7" t="s">
         <v>64</v>
@@ -8458,29 +8860,35 @@
       <c r="AC74" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE74" s="5" t="s">
-        <v>21</v>
+      <c r="AD74" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF74" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG74" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH74" s="5" t="s">
-        <v>21</v>
+      <c r="AG74" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH74" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI74" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ74" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="AK74" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="75" spans="1:37">
+      <c r="AJ74" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK74" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38">
+      <c r="B75" s="1">
+        <v>7</v>
+      </c>
       <c r="C75">
         <v>8</v>
       </c>
@@ -8541,8 +8949,8 @@
       <c r="Y75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA75" s="7" t="s">
-        <v>64</v>
+      <c r="Z75" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AB75" s="7" t="s">
         <v>64</v>
@@ -8550,29 +8958,35 @@
       <c r="AC75" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE75" s="5" t="s">
-        <v>21</v>
+      <c r="AD75" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG75" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH75" s="5" t="s">
-        <v>21</v>
+      <c r="AG75" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH75" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ75" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK75" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:37">
+      <c r="AJ75" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK75" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:38">
+      <c r="B76" s="1">
+        <v>7</v>
+      </c>
       <c r="C76">
         <v>9</v>
       </c>
@@ -8633,8 +9047,8 @@
       <c r="Y76" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA76" s="7" t="s">
-        <v>64</v>
+      <c r="Z76" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB76" s="7" t="s">
         <v>64</v>
@@ -8642,8 +9056,8 @@
       <c r="AC76" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE76" s="5" t="s">
-        <v>21</v>
+      <c r="AD76" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF76" s="5" t="s">
         <v>21</v>
@@ -8657,11 +9071,17 @@
       <c r="AI76" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ76" t="s">
+      <c r="AJ76" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK76" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:37">
+    <row r="77" spans="1:38">
+      <c r="B77" s="1">
+        <v>7</v>
+      </c>
       <c r="C77">
         <v>10</v>
       </c>
@@ -8722,8 +9142,8 @@
       <c r="Y77" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA77" s="7" t="s">
-        <v>64</v>
+      <c r="Z77" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB77" s="7" t="s">
         <v>64</v>
@@ -8731,8 +9151,8 @@
       <c r="AC77" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE77" s="5" t="s">
-        <v>21</v>
+      <c r="AD77" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF77" s="5" t="s">
         <v>21</v>
@@ -8743,17 +9163,23 @@
       <c r="AH77" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AI77" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ77" s="10" t="s">
+      <c r="AI77" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ77" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK77" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL77" t="s">
         <v>197</v>
       </c>
-      <c r="AK77" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" spans="1:37">
+    </row>
+    <row r="78" spans="1:38">
+      <c r="B78" s="1">
+        <v>7</v>
+      </c>
       <c r="C78">
         <v>11</v>
       </c>
@@ -8814,8 +9240,8 @@
       <c r="Y78" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA78" s="7" t="s">
-        <v>64</v>
+      <c r="Z78" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB78" s="7" t="s">
         <v>64</v>
@@ -8823,8 +9249,8 @@
       <c r="AC78" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE78" s="5" t="s">
-        <v>21</v>
+      <c r="AD78" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF78" s="5" t="s">
         <v>21</v>
@@ -8835,17 +9261,23 @@
       <c r="AH78" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AI78" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ78" s="1" t="s">
+      <c r="AI78" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ78" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK78" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AK78" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" spans="1:37">
+      <c r="AL78" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38">
+      <c r="B79" s="1">
+        <v>7</v>
+      </c>
       <c r="C79">
         <v>12</v>
       </c>
@@ -8906,8 +9338,8 @@
       <c r="Y79" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA79" s="7" t="s">
-        <v>64</v>
+      <c r="Z79" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB79" s="7" t="s">
         <v>64</v>
@@ -8915,8 +9347,8 @@
       <c r="AC79" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE79" s="5" t="s">
-        <v>21</v>
+      <c r="AD79" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF79" s="5" t="s">
         <v>21</v>
@@ -8930,11 +9362,17 @@
       <c r="AI79" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ79" t="s">
+      <c r="AJ79" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK79" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="80" spans="1:37">
+    <row r="80" spans="1:38">
+      <c r="B80" s="1">
+        <v>7</v>
+      </c>
       <c r="C80">
         <v>13</v>
       </c>
@@ -8995,8 +9433,8 @@
       <c r="Y80" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA80" s="7" t="s">
-        <v>64</v>
+      <c r="Z80" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB80" s="7" t="s">
         <v>64</v>
@@ -9004,14 +9442,14 @@
       <c r="AC80" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE80" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF80" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG80" s="5" t="s">
-        <v>21</v>
+      <c r="AD80" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF80" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG80" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH80" s="5" t="s">
         <v>21</v>
@@ -9019,14 +9457,20 @@
       <c r="AI80" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ80" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="AK80" t="s">
+      <c r="AJ80" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK80" s="10" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="81" spans="1:37">
+      <c r="AL80" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38">
+      <c r="B81" s="1">
+        <v>7</v>
+      </c>
       <c r="C81">
         <v>14</v>
       </c>
@@ -9087,8 +9531,8 @@
       <c r="Y81" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA81" s="7" t="s">
-        <v>64</v>
+      <c r="Z81" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB81" s="7" t="s">
         <v>64</v>
@@ -9096,14 +9540,14 @@
       <c r="AC81" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE81" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF81" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG81" s="5" t="s">
-        <v>21</v>
+      <c r="AD81" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF81" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG81" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH81" s="5" t="s">
         <v>21</v>
@@ -9111,14 +9555,20 @@
       <c r="AI81" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ81" s="1" t="s">
+      <c r="AJ81" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK81" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AK81" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" spans="1:37">
+      <c r="AL81" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38">
+      <c r="B82" s="1">
+        <v>7</v>
+      </c>
       <c r="C82">
         <v>15</v>
       </c>
@@ -9179,8 +9629,8 @@
       <c r="Y82" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA82" s="7" t="s">
-        <v>64</v>
+      <c r="Z82" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB82" s="7" t="s">
         <v>64</v>
@@ -9188,8 +9638,8 @@
       <c r="AC82" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE82" s="5" t="s">
-        <v>21</v>
+      <c r="AD82" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF82" s="5" t="s">
         <v>21</v>
@@ -9203,14 +9653,17 @@
       <c r="AI82" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ82" t="s">
+      <c r="AJ82" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK82" t="s">
         <v>45</v>
       </c>
-      <c r="AK82" t="s">
+      <c r="AL82" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:37">
+    <row r="84" spans="1:38">
       <c r="A84" s="1" t="s">
         <v>65</v>
       </c>
@@ -9277,8 +9730,8 @@
       <c r="Y84" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA84" t="s">
-        <v>22</v>
+      <c r="Z84" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB84" t="s">
         <v>22</v>
@@ -9286,8 +9739,8 @@
       <c r="AC84" t="s">
         <v>22</v>
       </c>
-      <c r="AE84" s="5" t="s">
-        <v>21</v>
+      <c r="AD84" t="s">
+        <v>22</v>
       </c>
       <c r="AF84" s="5" t="s">
         <v>21</v>
@@ -9301,11 +9754,17 @@
       <c r="AI84" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ84" t="s">
+      <c r="AJ84" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK84" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:37">
+    <row r="85" spans="1:38">
+      <c r="B85" s="1">
+        <v>8</v>
+      </c>
       <c r="C85">
         <v>1</v>
       </c>
@@ -9366,8 +9825,8 @@
       <c r="Y85" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA85" s="4" t="s">
-        <v>60</v>
+      <c r="Z85" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB85" s="4" t="s">
         <v>60</v>
@@ -9375,14 +9834,14 @@
       <c r="AC85" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE85" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF85" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG85" s="5" t="s">
-        <v>21</v>
+      <c r="AD85" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF85" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG85" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH85" s="5" t="s">
         <v>21</v>
@@ -9390,14 +9849,20 @@
       <c r="AI85" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ85" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="AK85" t="s">
+      <c r="AJ85" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK85" s="10" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="86" spans="1:37">
+      <c r="AL85" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38">
+      <c r="B86" s="1">
+        <v>8</v>
+      </c>
       <c r="C86">
         <v>2</v>
       </c>
@@ -9458,8 +9923,8 @@
       <c r="Y86" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA86" s="4" t="s">
-        <v>60</v>
+      <c r="Z86" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB86" s="4" t="s">
         <v>60</v>
@@ -9467,14 +9932,14 @@
       <c r="AC86" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE86" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF86" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG86" s="5" t="s">
-        <v>21</v>
+      <c r="AD86" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF86" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG86" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH86" s="5" t="s">
         <v>21</v>
@@ -9482,14 +9947,20 @@
       <c r="AI86" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ86" s="1" t="s">
+      <c r="AJ86" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK86" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AK86" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="87" spans="1:37">
+      <c r="AL86" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38">
+      <c r="B87" s="1">
+        <v>8</v>
+      </c>
       <c r="C87">
         <v>4</v>
       </c>
@@ -9550,8 +10021,8 @@
       <c r="Y87" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA87" s="4" t="s">
-        <v>60</v>
+      <c r="Z87" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB87" s="4" t="s">
         <v>60</v>
@@ -9559,8 +10030,8 @@
       <c r="AC87" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE87" s="5" t="s">
-        <v>21</v>
+      <c r="AD87" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF87" s="5" t="s">
         <v>21</v>
@@ -9574,11 +10045,17 @@
       <c r="AI87" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ87" t="s">
+      <c r="AJ87" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK87" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:37">
+    <row r="88" spans="1:38">
+      <c r="B88" s="1">
+        <v>8</v>
+      </c>
       <c r="C88">
         <v>5</v>
       </c>
@@ -9639,8 +10116,8 @@
       <c r="Y88" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA88" s="4" t="s">
-        <v>60</v>
+      <c r="Z88" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB88" s="4" t="s">
         <v>60</v>
@@ -9648,29 +10125,35 @@
       <c r="AC88" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE88" s="5" t="s">
-        <v>21</v>
+      <c r="AD88" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF88" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG88" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH88" s="5" t="s">
-        <v>21</v>
+      <c r="AG88" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH88" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI88" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ88" s="10" t="s">
+      <c r="AJ88" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK88" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="AL88" t="s">
         <v>203</v>
       </c>
-      <c r="AK88" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="89" spans="1:37">
+    </row>
+    <row r="89" spans="1:38">
+      <c r="B89" s="1">
+        <v>8</v>
+      </c>
       <c r="C89">
         <v>6</v>
       </c>
@@ -9731,8 +10214,8 @@
       <c r="Y89" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA89" s="4" t="s">
-        <v>60</v>
+      <c r="Z89" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB89" s="4" t="s">
         <v>60</v>
@@ -9740,29 +10223,35 @@
       <c r="AC89" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE89" s="5" t="s">
-        <v>21</v>
+      <c r="AD89" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF89" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG89" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH89" s="5" t="s">
-        <v>21</v>
+      <c r="AG89" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH89" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI89" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ89" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AK89" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="90" spans="1:37">
+      <c r="AJ89" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38">
+      <c r="B90" s="1">
+        <v>8</v>
+      </c>
       <c r="C90">
         <v>7</v>
       </c>
@@ -9823,8 +10312,8 @@
       <c r="Y90" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA90" s="4" t="s">
-        <v>60</v>
+      <c r="Z90" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB90" s="4" t="s">
         <v>60</v>
@@ -9832,8 +10321,8 @@
       <c r="AC90" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE90" s="5" t="s">
-        <v>21</v>
+      <c r="AD90" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF90" s="5" t="s">
         <v>21</v>
@@ -9847,11 +10336,17 @@
       <c r="AI90" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ90" t="s">
+      <c r="AJ90" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK90" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:37">
+    <row r="91" spans="1:38">
+      <c r="B91" s="1">
+        <v>8</v>
+      </c>
       <c r="C91">
         <v>8</v>
       </c>
@@ -9912,8 +10407,8 @@
       <c r="Y91" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA91" s="4" t="s">
-        <v>60</v>
+      <c r="Z91" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB91" s="4" t="s">
         <v>60</v>
@@ -9921,8 +10416,8 @@
       <c r="AC91" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE91" s="5" t="s">
-        <v>21</v>
+      <c r="AD91" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF91" s="5" t="s">
         <v>21</v>
@@ -9930,20 +10425,26 @@
       <c r="AG91" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AH91" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI91" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ91" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="AK91" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92" spans="1:37">
+      <c r="AH91" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI91" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ91" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK91" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38">
+      <c r="B92" s="1">
+        <v>8</v>
+      </c>
       <c r="C92">
         <v>9</v>
       </c>
@@ -10004,8 +10505,8 @@
       <c r="Y92" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA92" s="4" t="s">
-        <v>60</v>
+      <c r="Z92" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB92" s="4" t="s">
         <v>60</v>
@@ -10013,8 +10514,8 @@
       <c r="AC92" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE92" s="5" t="s">
-        <v>21</v>
+      <c r="AD92" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF92" s="5" t="s">
         <v>21</v>
@@ -10022,20 +10523,26 @@
       <c r="AG92" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AH92" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI92" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="AK92" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="93" spans="1:37">
+      <c r="AH92" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI92" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ92" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38">
+      <c r="B93" s="1">
+        <v>8</v>
+      </c>
       <c r="C93">
         <v>10</v>
       </c>
@@ -10096,8 +10603,8 @@
       <c r="Y93" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA93" s="4" t="s">
-        <v>60</v>
+      <c r="Z93" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB93" s="4" t="s">
         <v>60</v>
@@ -10105,8 +10612,8 @@
       <c r="AC93" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE93" s="5" t="s">
-        <v>21</v>
+      <c r="AD93" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF93" s="5" t="s">
         <v>21</v>
@@ -10120,11 +10627,17 @@
       <c r="AI93" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ93" t="s">
+      <c r="AJ93" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK93" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:37">
+    <row r="94" spans="1:38">
+      <c r="B94" s="1">
+        <v>8</v>
+      </c>
       <c r="C94">
         <v>11</v>
       </c>
@@ -10185,8 +10698,8 @@
       <c r="Y94" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA94" s="4" t="s">
-        <v>60</v>
+      <c r="Z94" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB94" s="4" t="s">
         <v>60</v>
@@ -10194,8 +10707,8 @@
       <c r="AC94" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE94" s="5" t="s">
-        <v>21</v>
+      <c r="AD94" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF94" s="5" t="s">
         <v>21</v>
@@ -10209,14 +10722,20 @@
       <c r="AI94" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ94" t="s">
-        <v>209</v>
+      <c r="AJ94" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AK94" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="95" spans="1:37">
+      <c r="AL94" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38">
+      <c r="B95" s="1">
+        <v>8</v>
+      </c>
       <c r="C95">
         <v>12</v>
       </c>
@@ -10277,8 +10796,8 @@
       <c r="Y95" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA95" s="4" t="s">
-        <v>60</v>
+      <c r="Z95" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB95" s="4" t="s">
         <v>60</v>
@@ -10286,8 +10805,8 @@
       <c r="AC95" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE95" s="5" t="s">
-        <v>21</v>
+      <c r="AD95" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF95" s="5" t="s">
         <v>21</v>
@@ -10301,14 +10820,20 @@
       <c r="AI95" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ95" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK95" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="96" spans="1:37">
+      <c r="AJ95" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK95" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38">
+      <c r="B96" s="1">
+        <v>8</v>
+      </c>
       <c r="C96">
         <v>13</v>
       </c>
@@ -10369,8 +10894,8 @@
       <c r="Y96" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA96" s="4" t="s">
-        <v>60</v>
+      <c r="Z96" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB96" s="4" t="s">
         <v>60</v>
@@ -10378,8 +10903,8 @@
       <c r="AC96" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE96" s="5" t="s">
-        <v>21</v>
+      <c r="AD96" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF96" s="5" t="s">
         <v>21</v>
@@ -10393,14 +10918,20 @@
       <c r="AI96" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ96" t="s">
+      <c r="AJ96" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK96" t="s">
         <v>26</v>
       </c>
-      <c r="AK96" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="97" spans="1:37">
+      <c r="AL96" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38">
+      <c r="B97" s="1">
+        <v>8</v>
+      </c>
       <c r="C97">
         <v>14</v>
       </c>
@@ -10461,8 +10992,8 @@
       <c r="Y97" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA97" s="4" t="s">
-        <v>60</v>
+      <c r="Z97" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB97" s="4" t="s">
         <v>60</v>
@@ -10470,8 +11001,8 @@
       <c r="AC97" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE97" s="5" t="s">
-        <v>21</v>
+      <c r="AD97" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF97" s="5" t="s">
         <v>21</v>
@@ -10485,14 +11016,20 @@
       <c r="AI97" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ97" t="s">
+      <c r="AJ97" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK97" t="s">
         <v>179</v>
       </c>
-      <c r="AK97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="98" spans="1:37">
+      <c r="AL97" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38">
+      <c r="B98" s="1">
+        <v>8</v>
+      </c>
       <c r="C98">
         <v>15</v>
       </c>
@@ -10553,8 +11090,8 @@
       <c r="Y98" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA98" s="4" t="s">
-        <v>60</v>
+      <c r="Z98" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB98" s="4" t="s">
         <v>60</v>
@@ -10562,8 +11099,8 @@
       <c r="AC98" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE98" s="5" t="s">
-        <v>21</v>
+      <c r="AD98" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF98" s="5" t="s">
         <v>21</v>
@@ -10577,14 +11114,20 @@
       <c r="AI98" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ98" s="1" t="s">
+      <c r="AJ98" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK98" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AK98" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" spans="1:37">
+      <c r="AL98" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38">
+      <c r="B99" s="1">
+        <v>8</v>
+      </c>
       <c r="C99">
         <v>16</v>
       </c>
@@ -10645,8 +11188,8 @@
       <c r="Y99" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA99" s="4" t="s">
-        <v>60</v>
+      <c r="Z99" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB99" s="4" t="s">
         <v>60</v>
@@ -10654,8 +11197,8 @@
       <c r="AC99" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE99" s="5" t="s">
-        <v>21</v>
+      <c r="AD99" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF99" s="5" t="s">
         <v>21</v>
@@ -10669,14 +11212,20 @@
       <c r="AI99" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ99" t="s">
+      <c r="AJ99" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK99" t="s">
         <v>26</v>
       </c>
-      <c r="AK99" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="100" spans="1:37">
+      <c r="AL99" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38">
+      <c r="B100" s="1">
+        <v>8</v>
+      </c>
       <c r="C100">
         <v>17</v>
       </c>
@@ -10737,8 +11286,8 @@
       <c r="Y100" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA100" s="4" t="s">
-        <v>60</v>
+      <c r="Z100" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB100" s="4" t="s">
         <v>60</v>
@@ -10746,29 +11295,35 @@
       <c r="AC100" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE100" s="5" t="s">
-        <v>21</v>
+      <c r="AD100" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF100" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG100" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH100" s="5" t="s">
-        <v>21</v>
+      <c r="AG100" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH100" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI100" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ100" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AK100" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="101" spans="1:37">
+      <c r="AJ100" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK100" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL100" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38">
+      <c r="B101" s="1">
+        <v>8</v>
+      </c>
       <c r="C101">
         <v>18</v>
       </c>
@@ -10829,8 +11384,8 @@
       <c r="Y101" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA101" s="4" t="s">
-        <v>60</v>
+      <c r="Z101" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB101" s="4" t="s">
         <v>60</v>
@@ -10838,29 +11393,35 @@
       <c r="AC101" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE101" s="5" t="s">
-        <v>21</v>
+      <c r="AD101" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF101" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG101" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH101" s="5" t="s">
-        <v>21</v>
+      <c r="AG101" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH101" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI101" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ101" s="1" t="s">
+      <c r="AJ101" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK101" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AK101" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="102" spans="1:37">
+      <c r="AL101" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38">
+      <c r="B102" s="1">
+        <v>8</v>
+      </c>
       <c r="C102">
         <v>19</v>
       </c>
@@ -10921,8 +11482,8 @@
       <c r="Y102" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA102" s="4" t="s">
-        <v>60</v>
+      <c r="Z102" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB102" s="4" t="s">
         <v>60</v>
@@ -10930,8 +11491,8 @@
       <c r="AC102" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE102" s="5" t="s">
-        <v>21</v>
+      <c r="AD102" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF102" s="5" t="s">
         <v>21</v>
@@ -10945,14 +11506,17 @@
       <c r="AI102" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ102" t="s">
+      <c r="AJ102" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK102" t="s">
         <v>45</v>
       </c>
-      <c r="AK102" t="s">
+      <c r="AL102" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:37">
+    <row r="104" spans="1:38">
       <c r="A104" s="1" t="s">
         <v>83</v>
       </c>
@@ -11019,8 +11583,8 @@
       <c r="Y104" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA104" t="s">
-        <v>22</v>
+      <c r="Z104" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB104" t="s">
         <v>22</v>
@@ -11028,8 +11592,8 @@
       <c r="AC104" t="s">
         <v>22</v>
       </c>
-      <c r="AE104" s="5" t="s">
-        <v>21</v>
+      <c r="AD104" t="s">
+        <v>22</v>
       </c>
       <c r="AF104" s="5" t="s">
         <v>21</v>
@@ -11043,14 +11607,20 @@
       <c r="AI104" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ104" t="s">
+      <c r="AJ104" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK104" t="s">
         <v>55</v>
       </c>
-      <c r="AK104" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="105" spans="1:37">
+      <c r="AL104" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38">
+      <c r="B105" s="1">
+        <v>9</v>
+      </c>
       <c r="C105">
         <v>1</v>
       </c>
@@ -11111,8 +11681,8 @@
       <c r="Y105" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA105" s="4" t="s">
-        <v>60</v>
+      <c r="Z105" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB105" s="4" t="s">
         <v>60</v>
@@ -11120,29 +11690,35 @@
       <c r="AC105" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE105" s="5" t="s">
-        <v>21</v>
+      <c r="AD105" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF105" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG105" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH105" s="5" t="s">
-        <v>21</v>
+      <c r="AG105" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH105" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI105" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ105" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK105" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="106" spans="1:37">
+      <c r="AJ105" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK105" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL105" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38">
+      <c r="B106" s="1">
+        <v>9</v>
+      </c>
       <c r="C106">
         <v>2</v>
       </c>
@@ -11203,8 +11779,8 @@
       <c r="Y106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA106" s="4" t="s">
-        <v>60</v>
+      <c r="Z106" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB106" s="4" t="s">
         <v>60</v>
@@ -11212,29 +11788,35 @@
       <c r="AC106" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE106" s="5" t="s">
-        <v>21</v>
+      <c r="AD106" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG106" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH106" s="5" t="s">
-        <v>21</v>
+      <c r="AG106" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH106" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI106" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ106" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AK106" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="107" spans="1:37">
+      <c r="AJ106" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK106" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38">
+      <c r="B107" s="1">
+        <v>9</v>
+      </c>
       <c r="C107">
         <v>3</v>
       </c>
@@ -11295,8 +11877,8 @@
       <c r="Y107" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA107" s="4" t="s">
-        <v>60</v>
+      <c r="Z107" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB107" s="4" t="s">
         <v>60</v>
@@ -11304,8 +11886,8 @@
       <c r="AC107" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE107" s="5" t="s">
-        <v>21</v>
+      <c r="AD107" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF107" s="5" t="s">
         <v>21</v>
@@ -11319,11 +11901,17 @@
       <c r="AI107" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ107" t="s">
+      <c r="AJ107" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK107" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:37">
+    <row r="108" spans="1:38">
+      <c r="B108" s="1">
+        <v>9</v>
+      </c>
       <c r="C108">
         <v>4</v>
       </c>
@@ -11384,8 +11972,8 @@
       <c r="Y108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA108" s="4" t="s">
-        <v>60</v>
+      <c r="Z108" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB108" s="4" t="s">
         <v>60</v>
@@ -11393,8 +11981,8 @@
       <c r="AC108" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE108" s="5" t="s">
-        <v>21</v>
+      <c r="AD108" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF108" s="5" t="s">
         <v>21</v>
@@ -11402,20 +11990,26 @@
       <c r="AG108" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AH108" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI108" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ108" s="10" t="s">
+      <c r="AH108" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI108" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ108" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK108" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="AL108" t="s">
         <v>215</v>
       </c>
-      <c r="AK108" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="109" spans="1:37">
+    </row>
+    <row r="109" spans="1:38">
+      <c r="B109" s="1">
+        <v>9</v>
+      </c>
       <c r="C109">
         <v>5</v>
       </c>
@@ -11476,8 +12070,8 @@
       <c r="Y109" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA109" s="4" t="s">
-        <v>60</v>
+      <c r="Z109" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB109" s="4" t="s">
         <v>60</v>
@@ -11485,8 +12079,8 @@
       <c r="AC109" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE109" s="5" t="s">
-        <v>21</v>
+      <c r="AD109" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF109" s="5" t="s">
         <v>21</v>
@@ -11500,14 +12094,20 @@
       <c r="AI109" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ109" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AK109" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="110" spans="1:37">
+      <c r="AJ109" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="AL109" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" spans="1:38">
+      <c r="B110" s="1">
+        <v>9</v>
+      </c>
       <c r="C110">
         <v>6</v>
       </c>
@@ -11568,8 +12168,8 @@
       <c r="Y110" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA110" s="4" t="s">
-        <v>60</v>
+      <c r="Z110" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB110" s="4" t="s">
         <v>60</v>
@@ -11577,8 +12177,8 @@
       <c r="AC110" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE110" s="5" t="s">
-        <v>21</v>
+      <c r="AD110" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF110" s="5" t="s">
         <v>21</v>
@@ -11592,11 +12192,17 @@
       <c r="AI110" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ110" t="s">
+      <c r="AJ110" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK110" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:37">
+    <row r="111" spans="1:38">
+      <c r="B111" s="1">
+        <v>9</v>
+      </c>
       <c r="C111">
         <v>7</v>
       </c>
@@ -11657,8 +12263,8 @@
       <c r="Y111" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA111" s="4" t="s">
-        <v>60</v>
+      <c r="Z111" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB111" s="4" t="s">
         <v>60</v>
@@ -11666,8 +12272,8 @@
       <c r="AC111" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE111" s="5" t="s">
-        <v>21</v>
+      <c r="AD111" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF111" s="5" t="s">
         <v>21</v>
@@ -11681,14 +12287,20 @@
       <c r="AI111" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ111" t="s">
-        <v>209</v>
+      <c r="AJ111" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AK111" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="112" spans="1:37">
+      <c r="AL111" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="112" spans="1:38">
+      <c r="B112" s="1">
+        <v>9</v>
+      </c>
       <c r="C112">
         <v>8</v>
       </c>
@@ -11749,8 +12361,8 @@
       <c r="Y112" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA112" s="4" t="s">
-        <v>60</v>
+      <c r="Z112" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB112" s="4" t="s">
         <v>60</v>
@@ -11758,8 +12370,8 @@
       <c r="AC112" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE112" s="5" t="s">
-        <v>21</v>
+      <c r="AD112" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF112" s="5" t="s">
         <v>21</v>
@@ -11773,14 +12385,20 @@
       <c r="AI112" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ112" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK112" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="113" spans="1:37">
+      <c r="AJ112" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK112" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL112" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38">
+      <c r="B113" s="1">
+        <v>9</v>
+      </c>
       <c r="C113">
         <v>9</v>
       </c>
@@ -11841,8 +12459,8 @@
       <c r="Y113" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA113" s="4" t="s">
-        <v>60</v>
+      <c r="Z113" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB113" s="4" t="s">
         <v>60</v>
@@ -11850,8 +12468,8 @@
       <c r="AC113" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE113" s="5" t="s">
-        <v>21</v>
+      <c r="AD113" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF113" s="5" t="s">
         <v>21</v>
@@ -11865,14 +12483,20 @@
       <c r="AI113" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ113" t="s">
+      <c r="AJ113" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK113" t="s">
         <v>26</v>
       </c>
-      <c r="AK113" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="114" spans="1:37">
+      <c r="AL113" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="114" spans="1:38">
+      <c r="B114" s="1">
+        <v>9</v>
+      </c>
       <c r="C114">
         <v>10</v>
       </c>
@@ -11933,8 +12557,8 @@
       <c r="Y114" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA114" s="4" t="s">
-        <v>60</v>
+      <c r="Z114" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB114" s="4" t="s">
         <v>60</v>
@@ -11942,8 +12566,8 @@
       <c r="AC114" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE114" s="5" t="s">
-        <v>21</v>
+      <c r="AD114" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF114" s="5" t="s">
         <v>21</v>
@@ -11957,14 +12581,20 @@
       <c r="AI114" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ114" t="s">
+      <c r="AJ114" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK114" t="s">
         <v>179</v>
       </c>
-      <c r="AK114" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="115" spans="1:37">
+      <c r="AL114" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38">
+      <c r="B115" s="1">
+        <v>9</v>
+      </c>
       <c r="C115">
         <v>11</v>
       </c>
@@ -12025,8 +12655,8 @@
       <c r="Y115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA115" s="4" t="s">
-        <v>60</v>
+      <c r="Z115" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB115" s="4" t="s">
         <v>60</v>
@@ -12034,8 +12664,8 @@
       <c r="AC115" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE115" s="5" t="s">
-        <v>21</v>
+      <c r="AD115" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF115" s="5" t="s">
         <v>21</v>
@@ -12049,14 +12679,20 @@
       <c r="AI115" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ115" s="1" t="s">
+      <c r="AJ115" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK115" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AK115" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="116" spans="1:37">
+      <c r="AL115" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38">
+      <c r="B116" s="1">
+        <v>9</v>
+      </c>
       <c r="C116">
         <v>12</v>
       </c>
@@ -12117,8 +12753,8 @@
       <c r="Y116" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA116" s="4" t="s">
-        <v>60</v>
+      <c r="Z116" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB116" s="4" t="s">
         <v>60</v>
@@ -12126,8 +12762,8 @@
       <c r="AC116" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE116" s="5" t="s">
-        <v>21</v>
+      <c r="AD116" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF116" s="5" t="s">
         <v>21</v>
@@ -12141,14 +12777,20 @@
       <c r="AI116" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ116" t="s">
+      <c r="AJ116" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK116" t="s">
         <v>26</v>
       </c>
-      <c r="AK116" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="117" spans="1:37">
+      <c r="AL116" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38">
+      <c r="B117" s="1">
+        <v>9</v>
+      </c>
       <c r="C117">
         <v>13</v>
       </c>
@@ -12209,8 +12851,8 @@
       <c r="Y117" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA117" s="4" t="s">
-        <v>60</v>
+      <c r="Z117" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB117" s="4" t="s">
         <v>60</v>
@@ -12218,29 +12860,35 @@
       <c r="AC117" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE117" s="5" t="s">
-        <v>21</v>
+      <c r="AD117" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF117" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG117" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH117" s="5" t="s">
-        <v>21</v>
+      <c r="AG117" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH117" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI117" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ117" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AK117" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="118" spans="1:37">
+      <c r="AJ117" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK117" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38">
+      <c r="B118" s="1">
+        <v>9</v>
+      </c>
       <c r="C118">
         <v>14</v>
       </c>
@@ -12301,8 +12949,8 @@
       <c r="Y118" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA118" s="4" t="s">
-        <v>60</v>
+      <c r="Z118" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB118" s="4" t="s">
         <v>60</v>
@@ -12310,29 +12958,35 @@
       <c r="AC118" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE118" s="5" t="s">
-        <v>21</v>
+      <c r="AD118" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF118" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG118" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH118" s="5" t="s">
-        <v>21</v>
+      <c r="AG118" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH118" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI118" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ118" s="1" t="s">
+      <c r="AJ118" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK118" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AK118" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="119" spans="1:37">
+      <c r="AL118" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38">
+      <c r="B119" s="1">
+        <v>9</v>
+      </c>
       <c r="C119">
         <v>15</v>
       </c>
@@ -12393,8 +13047,8 @@
       <c r="Y119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA119" s="4" t="s">
-        <v>60</v>
+      <c r="Z119" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB119" s="4" t="s">
         <v>60</v>
@@ -12402,8 +13056,8 @@
       <c r="AC119" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE119" s="5" t="s">
-        <v>21</v>
+      <c r="AD119" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="AF119" s="5" t="s">
         <v>21</v>
@@ -12417,14 +13071,17 @@
       <c r="AI119" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ119" t="s">
+      <c r="AJ119" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK119" t="s">
         <v>26</v>
       </c>
-      <c r="AK119" t="s">
+      <c r="AL119" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="121" spans="1:37">
+    <row r="121" spans="1:38">
       <c r="A121" s="1" t="s">
         <v>91</v>
       </c>
@@ -12491,8 +13148,8 @@
       <c r="Y121" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA121" t="s">
-        <v>22</v>
+      <c r="Z121" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB121" t="s">
         <v>22</v>
@@ -12500,8 +13157,8 @@
       <c r="AC121" t="s">
         <v>22</v>
       </c>
-      <c r="AE121" s="5" t="s">
-        <v>21</v>
+      <c r="AD121" t="s">
+        <v>22</v>
       </c>
       <c r="AF121" s="5" t="s">
         <v>21</v>
@@ -12515,11 +13172,17 @@
       <c r="AI121" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ121" t="s">
+      <c r="AJ121" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK121" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:37">
+    <row r="122" spans="1:38">
+      <c r="B122" s="1">
+        <v>10</v>
+      </c>
       <c r="C122">
         <v>1</v>
       </c>
@@ -12580,8 +13243,8 @@
       <c r="Y122" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA122" s="7" t="s">
-        <v>64</v>
+      <c r="Z122" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB122" s="7" t="s">
         <v>64</v>
@@ -12589,29 +13252,35 @@
       <c r="AC122" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE122" s="5" t="s">
-        <v>21</v>
+      <c r="AD122" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF122" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG122" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH122" s="5" t="s">
-        <v>21</v>
+      <c r="AG122" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH122" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI122" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ122" s="10" t="s">
+      <c r="AJ122" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK122" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AK122" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="123" spans="1:37">
+      <c r="AL122" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38">
+      <c r="B123" s="1">
+        <v>10</v>
+      </c>
       <c r="C123">
         <v>2</v>
       </c>
@@ -12672,8 +13341,8 @@
       <c r="Y123" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA123" s="7" t="s">
-        <v>64</v>
+      <c r="Z123" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB123" s="7" t="s">
         <v>64</v>
@@ -12681,29 +13350,35 @@
       <c r="AC123" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE123" s="5" t="s">
-        <v>21</v>
+      <c r="AD123" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF123" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG123" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH123" s="5" t="s">
-        <v>21</v>
+      <c r="AG123" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH123" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI123" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ123" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK123" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="124" spans="1:37">
+      <c r="AJ123" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK123" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL123" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38">
+      <c r="B124" s="1">
+        <v>10</v>
+      </c>
       <c r="C124">
         <v>3</v>
       </c>
@@ -12764,8 +13439,8 @@
       <c r="Y124" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA124" s="7" t="s">
-        <v>64</v>
+      <c r="Z124" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB124" s="7" t="s">
         <v>64</v>
@@ -12773,8 +13448,8 @@
       <c r="AC124" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE124" s="5" t="s">
-        <v>21</v>
+      <c r="AD124" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF124" s="5" t="s">
         <v>21</v>
@@ -12788,14 +13463,20 @@
       <c r="AI124" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ124" t="s">
+      <c r="AJ124" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK124" t="s">
         <v>26</v>
       </c>
-      <c r="AK124" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="125" spans="1:37">
+      <c r="AL124" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38">
+      <c r="B125" s="1">
+        <v>10</v>
+      </c>
       <c r="C125">
         <v>4</v>
       </c>
@@ -12856,8 +13537,8 @@
       <c r="Y125" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA125" s="7" t="s">
-        <v>64</v>
+      <c r="Z125" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB125" s="7" t="s">
         <v>64</v>
@@ -12865,8 +13546,8 @@
       <c r="AC125" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE125" s="5" t="s">
-        <v>21</v>
+      <c r="AD125" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF125" s="5" t="s">
         <v>21</v>
@@ -12880,14 +13561,20 @@
       <c r="AI125" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ125" t="s">
+      <c r="AJ125" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK125" t="s">
         <v>179</v>
       </c>
-      <c r="AK125" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="126" spans="1:37">
+      <c r="AL125" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38">
+      <c r="B126" s="1">
+        <v>10</v>
+      </c>
       <c r="C126">
         <v>5</v>
       </c>
@@ -12948,8 +13635,8 @@
       <c r="Y126" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA126" s="7" t="s">
-        <v>64</v>
+      <c r="Z126" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB126" s="7" t="s">
         <v>64</v>
@@ -12957,8 +13644,8 @@
       <c r="AC126" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE126" s="5" t="s">
-        <v>21</v>
+      <c r="AD126" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF126" s="5" t="s">
         <v>21</v>
@@ -12972,14 +13659,20 @@
       <c r="AI126" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ126" s="1" t="s">
+      <c r="AJ126" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK126" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AK126" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="127" spans="1:37">
+      <c r="AL126" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38">
+      <c r="B127" s="1">
+        <v>10</v>
+      </c>
       <c r="C127">
         <v>6</v>
       </c>
@@ -13040,8 +13733,8 @@
       <c r="Y127" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA127" s="7" t="s">
-        <v>64</v>
+      <c r="Z127" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB127" s="7" t="s">
         <v>64</v>
@@ -13049,8 +13742,8 @@
       <c r="AC127" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE127" s="5" t="s">
-        <v>21</v>
+      <c r="AD127" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF127" s="5" t="s">
         <v>21</v>
@@ -13064,14 +13757,20 @@
       <c r="AI127" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ127" t="s">
+      <c r="AJ127" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK127" t="s">
         <v>26</v>
       </c>
-      <c r="AK127" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="128" spans="1:37">
+      <c r="AL127" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38">
+      <c r="B128" s="1">
+        <v>10</v>
+      </c>
       <c r="C128">
         <v>7</v>
       </c>
@@ -13132,8 +13831,8 @@
       <c r="Y128" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA128" s="7" t="s">
-        <v>64</v>
+      <c r="Z128" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AB128" s="7" t="s">
         <v>64</v>
@@ -13141,29 +13840,35 @@
       <c r="AC128" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE128" s="5" t="s">
-        <v>21</v>
+      <c r="AD128" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF128" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG128" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH128" s="5" t="s">
-        <v>21</v>
+      <c r="AG128" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH128" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI128" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ128" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="AK128" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="129" spans="1:37">
+      <c r="AJ128" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK128" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="AL128" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="129" spans="1:38">
+      <c r="B129" s="1">
+        <v>10</v>
+      </c>
       <c r="C129">
         <v>8</v>
       </c>
@@ -13224,8 +13929,8 @@
       <c r="Y129" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA129" s="7" t="s">
-        <v>64</v>
+      <c r="Z129" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AB129" s="7" t="s">
         <v>64</v>
@@ -13233,29 +13938,35 @@
       <c r="AC129" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE129" s="5" t="s">
-        <v>21</v>
+      <c r="AD129" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF129" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG129" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH129" s="5" t="s">
-        <v>21</v>
+      <c r="AG129" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH129" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI129" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ129" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK129" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="130" spans="1:37">
+      <c r="AJ129" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK129" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AL129" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="130" spans="1:38">
+      <c r="B130" s="1">
+        <v>10</v>
+      </c>
       <c r="C130">
         <v>9</v>
       </c>
@@ -13316,8 +14027,8 @@
       <c r="Y130" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA130" s="7" t="s">
-        <v>64</v>
+      <c r="Z130" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB130" s="7" t="s">
         <v>64</v>
@@ -13325,8 +14036,8 @@
       <c r="AC130" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE130" s="5" t="s">
-        <v>21</v>
+      <c r="AD130" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF130" s="5" t="s">
         <v>21</v>
@@ -13340,11 +14051,17 @@
       <c r="AI130" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ130" t="s">
+      <c r="AJ130" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK130" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:37">
+    <row r="131" spans="1:38">
+      <c r="B131" s="1">
+        <v>10</v>
+      </c>
       <c r="C131">
         <v>10</v>
       </c>
@@ -13405,8 +14122,8 @@
       <c r="Y131" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA131" s="7" t="s">
-        <v>64</v>
+      <c r="Z131" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB131" s="7" t="s">
         <v>64</v>
@@ -13414,8 +14131,8 @@
       <c r="AC131" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE131" s="5" t="s">
-        <v>21</v>
+      <c r="AD131" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF131" s="5" t="s">
         <v>21</v>
@@ -13426,17 +14143,23 @@
       <c r="AH131" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AI131" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ131" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="AK131" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="132" spans="1:37">
+      <c r="AI131" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ131" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK131" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="AL131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38">
+      <c r="B132" s="1">
+        <v>10</v>
+      </c>
       <c r="C132">
         <v>11</v>
       </c>
@@ -13497,8 +14220,8 @@
       <c r="Y132" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA132" s="7" t="s">
-        <v>64</v>
+      <c r="Z132" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB132" s="7" t="s">
         <v>64</v>
@@ -13506,8 +14229,8 @@
       <c r="AC132" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE132" s="5" t="s">
-        <v>21</v>
+      <c r="AD132" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF132" s="5" t="s">
         <v>21</v>
@@ -13518,17 +14241,23 @@
       <c r="AH132" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AI132" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ132" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="AK132" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="133" spans="1:37">
+      <c r="AI132" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ132" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK132" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AL132" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="133" spans="1:38">
+      <c r="B133" s="1">
+        <v>10</v>
+      </c>
       <c r="C133">
         <v>12</v>
       </c>
@@ -13589,8 +14318,8 @@
       <c r="Y133" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA133" s="7" t="s">
-        <v>64</v>
+      <c r="Z133" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB133" s="7" t="s">
         <v>64</v>
@@ -13598,8 +14327,8 @@
       <c r="AC133" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE133" s="5" t="s">
-        <v>21</v>
+      <c r="AD133" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF133" s="5" t="s">
         <v>21</v>
@@ -13613,14 +14342,17 @@
       <c r="AI133" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ133" t="s">
+      <c r="AJ133" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK133" t="s">
         <v>26</v>
       </c>
-      <c r="AK133" t="s">
+      <c r="AL133" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="135" spans="1:37">
+    <row r="135" spans="1:38">
       <c r="A135" s="1" t="s">
         <v>171</v>
       </c>
@@ -13687,8 +14419,8 @@
       <c r="Y135" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA135" t="s">
-        <v>22</v>
+      <c r="Z135" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB135" t="s">
         <v>22</v>
@@ -13696,8 +14428,8 @@
       <c r="AC135" t="s">
         <v>22</v>
       </c>
-      <c r="AE135" s="5" t="s">
-        <v>21</v>
+      <c r="AD135" t="s">
+        <v>22</v>
       </c>
       <c r="AF135" s="5" t="s">
         <v>21</v>
@@ -13711,11 +14443,17 @@
       <c r="AI135" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ135" t="s">
+      <c r="AJ135" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK135" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="136" spans="1:37">
+    <row r="136" spans="1:38">
+      <c r="B136" s="1">
+        <v>11</v>
+      </c>
       <c r="C136">
         <v>1</v>
       </c>
@@ -13776,8 +14514,8 @@
       <c r="Y136" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA136" t="s">
-        <v>22</v>
+      <c r="Z136" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB136" t="s">
         <v>22</v>
@@ -13785,14 +14523,14 @@
       <c r="AC136" t="s">
         <v>22</v>
       </c>
-      <c r="AE136" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF136" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG136" s="5" t="s">
-        <v>21</v>
+      <c r="AD136" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF136" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG136" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH136" s="5" t="s">
         <v>21</v>
@@ -13800,14 +14538,20 @@
       <c r="AI136" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ136" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="AK136" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="137" spans="1:37">
+      <c r="AJ136" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK136" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="AL136" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38">
+      <c r="B137" s="1">
+        <v>11</v>
+      </c>
       <c r="C137">
         <v>2</v>
       </c>
@@ -13868,8 +14612,8 @@
       <c r="Y137" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA137" t="s">
-        <v>22</v>
+      <c r="Z137" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB137" t="s">
         <v>22</v>
@@ -13877,14 +14621,14 @@
       <c r="AC137" t="s">
         <v>22</v>
       </c>
-      <c r="AE137" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF137" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG137" s="5" t="s">
-        <v>21</v>
+      <c r="AD137" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF137" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG137" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH137" s="5" t="s">
         <v>21</v>
@@ -13892,14 +14636,20 @@
       <c r="AI137" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ137" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="AK137" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="138" spans="1:37">
+      <c r="AJ137" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK137" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="AL137" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="138" spans="1:38">
+      <c r="B138" s="1">
+        <v>11</v>
+      </c>
       <c r="C138">
         <v>3</v>
       </c>
@@ -13960,8 +14710,8 @@
       <c r="Y138" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA138" t="s">
-        <v>22</v>
+      <c r="Z138" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB138" t="s">
         <v>22</v>
@@ -13969,8 +14719,8 @@
       <c r="AC138" t="s">
         <v>22</v>
       </c>
-      <c r="AE138" s="5" t="s">
-        <v>21</v>
+      <c r="AD138" t="s">
+        <v>22</v>
       </c>
       <c r="AF138" s="5" t="s">
         <v>21</v>
@@ -13984,11 +14734,17 @@
       <c r="AI138" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ138" t="s">
+      <c r="AJ138" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK138" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:37">
+    <row r="139" spans="1:38">
+      <c r="B139" s="1">
+        <v>11</v>
+      </c>
       <c r="C139">
         <v>4</v>
       </c>
@@ -14049,8 +14805,8 @@
       <c r="Y139" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA139" t="s">
-        <v>22</v>
+      <c r="Z139" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB139" t="s">
         <v>22</v>
@@ -14058,11 +14814,11 @@
       <c r="AC139" t="s">
         <v>22</v>
       </c>
-      <c r="AE139" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF139" s="5" t="s">
-        <v>21</v>
+      <c r="AD139" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF139" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG139" s="5" t="s">
         <v>21</v>
@@ -14073,14 +14829,20 @@
       <c r="AI139" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ139" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="AK139" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="140" spans="1:37">
+      <c r="AJ139" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK139" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="AL139" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38">
+      <c r="B140" s="1">
+        <v>11</v>
+      </c>
       <c r="C140">
         <v>5</v>
       </c>
@@ -14141,8 +14903,8 @@
       <c r="Y140" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA140" t="s">
-        <v>22</v>
+      <c r="Z140" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB140" t="s">
         <v>22</v>
@@ -14150,11 +14912,11 @@
       <c r="AC140" t="s">
         <v>22</v>
       </c>
-      <c r="AE140" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF140" s="5" t="s">
-        <v>21</v>
+      <c r="AD140" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF140" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG140" s="5" t="s">
         <v>21</v>
@@ -14165,14 +14927,20 @@
       <c r="AI140" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ140" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="AK140" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="141" spans="1:37">
+      <c r="AJ140" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK140" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AL140" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38">
+      <c r="B141" s="1">
+        <v>11</v>
+      </c>
       <c r="C141">
         <v>6</v>
       </c>
@@ -14233,8 +15001,8 @@
       <c r="Y141" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA141" t="s">
-        <v>22</v>
+      <c r="Z141" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB141" t="s">
         <v>22</v>
@@ -14242,8 +15010,8 @@
       <c r="AC141" t="s">
         <v>22</v>
       </c>
-      <c r="AE141" s="5" t="s">
-        <v>21</v>
+      <c r="AD141" t="s">
+        <v>22</v>
       </c>
       <c r="AF141" s="5" t="s">
         <v>21</v>
@@ -14257,14 +15025,17 @@
       <c r="AI141" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ141" t="s">
+      <c r="AJ141" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK141" t="s">
         <v>45</v>
       </c>
-      <c r="AK141" t="s">
+      <c r="AL141" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="143" spans="1:37">
+    <row r="143" spans="1:38">
       <c r="A143" s="1" t="s">
         <v>172</v>
       </c>
@@ -14331,8 +15102,8 @@
       <c r="Y143" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA143" t="s">
-        <v>22</v>
+      <c r="Z143" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB143" t="s">
         <v>22</v>
@@ -14340,8 +15111,8 @@
       <c r="AC143" t="s">
         <v>22</v>
       </c>
-      <c r="AE143" s="5" t="s">
-        <v>21</v>
+      <c r="AD143" t="s">
+        <v>22</v>
       </c>
       <c r="AF143" s="5" t="s">
         <v>21</v>
@@ -14355,11 +15126,17 @@
       <c r="AI143" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ143" t="s">
+      <c r="AJ143" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK143" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="144" spans="1:37">
+    <row r="144" spans="1:38">
+      <c r="B144" s="1">
+        <v>12</v>
+      </c>
       <c r="C144">
         <v>1</v>
       </c>
@@ -14420,8 +15197,8 @@
       <c r="Y144" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA144" t="s">
-        <v>22</v>
+      <c r="Z144" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB144" t="s">
         <v>22</v>
@@ -14429,11 +15206,11 @@
       <c r="AC144" t="s">
         <v>22</v>
       </c>
-      <c r="AE144" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF144" s="5" t="s">
-        <v>21</v>
+      <c r="AD144" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF144" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG144" s="5" t="s">
         <v>21</v>
@@ -14444,14 +15221,20 @@
       <c r="AI144" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ144" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="AK144" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="145" spans="1:37">
+      <c r="AJ144" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK144" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="AL144" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="145" spans="1:38">
+      <c r="B145" s="1">
+        <v>12</v>
+      </c>
       <c r="C145">
         <v>2</v>
       </c>
@@ -14512,8 +15295,8 @@
       <c r="Y145" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA145" t="s">
-        <v>22</v>
+      <c r="Z145" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB145" t="s">
         <v>22</v>
@@ -14521,11 +15304,11 @@
       <c r="AC145" t="s">
         <v>22</v>
       </c>
-      <c r="AE145" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF145" s="5" t="s">
-        <v>21</v>
+      <c r="AD145" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF145" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AG145" s="5" t="s">
         <v>21</v>
@@ -14536,14 +15319,20 @@
       <c r="AI145" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ145" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="AK145" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="146" spans="1:37">
+      <c r="AJ145" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK145" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AL145" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="146" spans="1:38">
+      <c r="B146" s="1">
+        <v>12</v>
+      </c>
       <c r="C146">
         <v>3</v>
       </c>
@@ -14604,8 +15393,8 @@
       <c r="Y146" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA146" t="s">
-        <v>22</v>
+      <c r="Z146" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB146" t="s">
         <v>22</v>
@@ -14613,8 +15402,8 @@
       <c r="AC146" t="s">
         <v>22</v>
       </c>
-      <c r="AE146" s="5" t="s">
-        <v>21</v>
+      <c r="AD146" t="s">
+        <v>22</v>
       </c>
       <c r="AF146" s="5" t="s">
         <v>21</v>
@@ -14628,11 +15417,17 @@
       <c r="AI146" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ146" t="s">
+      <c r="AJ146" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK146" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:37">
+    <row r="147" spans="1:38">
+      <c r="B147" s="1">
+        <v>12</v>
+      </c>
       <c r="C147">
         <v>4</v>
       </c>
@@ -14693,8 +15488,8 @@
       <c r="Y147" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA147" t="s">
-        <v>22</v>
+      <c r="Z147" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB147" t="s">
         <v>22</v>
@@ -14702,14 +15497,14 @@
       <c r="AC147" t="s">
         <v>22</v>
       </c>
-      <c r="AE147" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF147" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG147" s="5" t="s">
-        <v>21</v>
+      <c r="AD147" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF147" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG147" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH147" s="5" t="s">
         <v>21</v>
@@ -14717,14 +15512,20 @@
       <c r="AI147" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ147" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="AK147" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="148" spans="1:37">
+      <c r="AJ147" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK147" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="AL147" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="148" spans="1:38">
+      <c r="B148" s="1">
+        <v>12</v>
+      </c>
       <c r="C148">
         <v>5</v>
       </c>
@@ -14785,8 +15586,8 @@
       <c r="Y148" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA148" t="s">
-        <v>22</v>
+      <c r="Z148" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB148" t="s">
         <v>22</v>
@@ -14794,14 +15595,14 @@
       <c r="AC148" t="s">
         <v>22</v>
       </c>
-      <c r="AE148" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF148" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG148" s="5" t="s">
-        <v>21</v>
+      <c r="AD148" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF148" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG148" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH148" s="5" t="s">
         <v>21</v>
@@ -14809,14 +15610,20 @@
       <c r="AI148" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ148" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="AK148" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="149" spans="1:37">
+      <c r="AJ148" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK148" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL148" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="149" spans="1:38">
+      <c r="B149" s="1">
+        <v>12</v>
+      </c>
       <c r="C149">
         <v>6</v>
       </c>
@@ -14877,8 +15684,8 @@
       <c r="Y149" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA149" t="s">
-        <v>22</v>
+      <c r="Z149" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB149" t="s">
         <v>22</v>
@@ -14886,8 +15693,8 @@
       <c r="AC149" t="s">
         <v>22</v>
       </c>
-      <c r="AE149" s="5" t="s">
-        <v>21</v>
+      <c r="AD149" t="s">
+        <v>22</v>
       </c>
       <c r="AF149" s="5" t="s">
         <v>21</v>
@@ -14901,14 +15708,17 @@
       <c r="AI149" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ149" t="s">
+      <c r="AJ149" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK149" t="s">
         <v>45</v>
       </c>
-      <c r="AK149" t="s">
+      <c r="AL149" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:37">
+    <row r="151" spans="1:38">
       <c r="A151" s="1" t="s">
         <v>137</v>
       </c>
@@ -14975,8 +15785,8 @@
       <c r="Y151" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA151" t="s">
-        <v>22</v>
+      <c r="Z151" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB151" t="s">
         <v>22</v>
@@ -14984,8 +15794,8 @@
       <c r="AC151" t="s">
         <v>22</v>
       </c>
-      <c r="AE151" s="5" t="s">
-        <v>21</v>
+      <c r="AD151" t="s">
+        <v>22</v>
       </c>
       <c r="AF151" s="5" t="s">
         <v>21</v>
@@ -14999,11 +15809,17 @@
       <c r="AI151" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ151" t="s">
+      <c r="AJ151" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK151" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="152" spans="1:37">
+    <row r="152" spans="1:38">
+      <c r="B152" s="1">
+        <v>13</v>
+      </c>
       <c r="C152">
         <v>1</v>
       </c>
@@ -15064,8 +15880,8 @@
       <c r="Y152" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA152" t="s">
-        <v>22</v>
+      <c r="Z152" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB152" t="s">
         <v>22</v>
@@ -15073,8 +15889,8 @@
       <c r="AC152" t="s">
         <v>22</v>
       </c>
-      <c r="AE152" s="5" t="s">
-        <v>21</v>
+      <c r="AD152" t="s">
+        <v>22</v>
       </c>
       <c r="AF152" s="5" t="s">
         <v>21</v>
@@ -15088,14 +15904,17 @@
       <c r="AI152" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ152" t="s">
+      <c r="AJ152" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK152" t="s">
         <v>28</v>
       </c>
-      <c r="AK152" t="s">
+      <c r="AL152" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:37">
+    <row r="154" spans="1:38">
       <c r="A154" s="1" t="s">
         <v>146</v>
       </c>
@@ -15162,8 +15981,8 @@
       <c r="Y154" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA154" t="s">
-        <v>22</v>
+      <c r="Z154" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB154" t="s">
         <v>22</v>
@@ -15171,8 +15990,8 @@
       <c r="AC154" t="s">
         <v>22</v>
       </c>
-      <c r="AE154" s="5" t="s">
-        <v>21</v>
+      <c r="AD154" t="s">
+        <v>22</v>
       </c>
       <c r="AF154" s="5" t="s">
         <v>21</v>
@@ -15186,11 +16005,17 @@
       <c r="AI154" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ154" t="s">
+      <c r="AJ154" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK154" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="155" spans="1:37">
+    <row r="155" spans="1:38">
+      <c r="B155" s="1">
+        <v>14</v>
+      </c>
       <c r="C155">
         <v>1</v>
       </c>
@@ -15251,8 +16076,8 @@
       <c r="Y155" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA155" t="s">
-        <v>22</v>
+      <c r="Z155" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB155" t="s">
         <v>22</v>
@@ -15260,14 +16085,14 @@
       <c r="AC155" t="s">
         <v>22</v>
       </c>
-      <c r="AE155" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF155" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG155" s="5" t="s">
-        <v>21</v>
+      <c r="AD155" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF155" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG155" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH155" s="5" t="s">
         <v>21</v>
@@ -15275,11 +16100,17 @@
       <c r="AI155" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ155" s="9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="156" spans="1:37">
+      <c r="AJ155" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK155" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="156" spans="1:38">
+      <c r="B156" s="1">
+        <v>14</v>
+      </c>
       <c r="C156">
         <v>2</v>
       </c>
@@ -15340,8 +16171,8 @@
       <c r="Y156" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA156" t="s">
-        <v>22</v>
+      <c r="Z156" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB156" t="s">
         <v>22</v>
@@ -15349,14 +16180,14 @@
       <c r="AC156" t="s">
         <v>22</v>
       </c>
-      <c r="AE156" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF156" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG156" s="5" t="s">
-        <v>21</v>
+      <c r="AD156" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF156" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG156" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH156" s="5" t="s">
         <v>21</v>
@@ -15364,11 +16195,17 @@
       <c r="AI156" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ156" s="1" t="s">
+      <c r="AJ156" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK156" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="157" spans="1:37">
+    <row r="157" spans="1:38">
+      <c r="B157" s="1">
+        <v>14</v>
+      </c>
       <c r="C157">
         <v>3</v>
       </c>
@@ -15429,8 +16266,8 @@
       <c r="Y157" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA157" t="s">
-        <v>22</v>
+      <c r="Z157" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB157" t="s">
         <v>22</v>
@@ -15438,8 +16275,8 @@
       <c r="AC157" t="s">
         <v>22</v>
       </c>
-      <c r="AE157" s="5" t="s">
-        <v>21</v>
+      <c r="AD157" t="s">
+        <v>22</v>
       </c>
       <c r="AF157" s="5" t="s">
         <v>21</v>
@@ -15453,11 +16290,17 @@
       <c r="AI157" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ157" t="s">
+      <c r="AJ157" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK157" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:37">
+    <row r="158" spans="1:38">
+      <c r="B158" s="1">
+        <v>14</v>
+      </c>
       <c r="C158">
         <v>4</v>
       </c>
@@ -15518,8 +16361,8 @@
       <c r="Y158" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA158" t="s">
-        <v>22</v>
+      <c r="Z158" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB158" t="s">
         <v>22</v>
@@ -15527,26 +16370,32 @@
       <c r="AC158" t="s">
         <v>22</v>
       </c>
-      <c r="AE158" s="5" t="s">
-        <v>21</v>
+      <c r="AD158" t="s">
+        <v>22</v>
       </c>
       <c r="AF158" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG158" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH158" s="5" t="s">
-        <v>21</v>
+      <c r="AG158" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH158" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI158" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ158" s="9" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="159" spans="1:37">
+      <c r="AJ158" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK158" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="159" spans="1:38">
+      <c r="B159" s="1">
+        <v>14</v>
+      </c>
       <c r="C159">
         <v>5</v>
       </c>
@@ -15607,8 +16456,8 @@
       <c r="Y159" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA159" t="s">
-        <v>22</v>
+      <c r="Z159" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB159" t="s">
         <v>22</v>
@@ -15616,26 +16465,32 @@
       <c r="AC159" t="s">
         <v>22</v>
       </c>
-      <c r="AE159" s="5" t="s">
-        <v>21</v>
+      <c r="AD159" t="s">
+        <v>22</v>
       </c>
       <c r="AF159" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG159" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH159" s="5" t="s">
-        <v>21</v>
+      <c r="AG159" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH159" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI159" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ159" s="1" t="s">
+      <c r="AJ159" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK159" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="160" spans="1:37">
+    <row r="160" spans="1:38">
+      <c r="B160" s="1">
+        <v>14</v>
+      </c>
       <c r="C160">
         <v>6</v>
       </c>
@@ -15696,8 +16551,8 @@
       <c r="Y160" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA160" t="s">
-        <v>22</v>
+      <c r="Z160" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB160" t="s">
         <v>22</v>
@@ -15705,8 +16560,8 @@
       <c r="AC160" t="s">
         <v>22</v>
       </c>
-      <c r="AE160" s="5" t="s">
-        <v>21</v>
+      <c r="AD160" t="s">
+        <v>22</v>
       </c>
       <c r="AF160" s="5" t="s">
         <v>21</v>
@@ -15720,14 +16575,17 @@
       <c r="AI160" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ160" t="s">
+      <c r="AJ160" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK160" t="s">
         <v>45</v>
       </c>
-      <c r="AK160" t="s">
+      <c r="AL160" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:37">
+    <row r="162" spans="1:38">
       <c r="A162" s="1" t="s">
         <v>138</v>
       </c>
@@ -15794,8 +16652,8 @@
       <c r="Y162" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA162" t="s">
-        <v>22</v>
+      <c r="Z162" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB162" t="s">
         <v>22</v>
@@ -15803,8 +16661,8 @@
       <c r="AC162" t="s">
         <v>22</v>
       </c>
-      <c r="AE162" s="5" t="s">
-        <v>21</v>
+      <c r="AD162" t="s">
+        <v>22</v>
       </c>
       <c r="AF162" s="5" t="s">
         <v>21</v>
@@ -15818,11 +16676,17 @@
       <c r="AI162" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ162" t="s">
+      <c r="AJ162" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK162" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="163" spans="1:37">
+    <row r="163" spans="1:38">
+      <c r="B163" s="1">
+        <v>15</v>
+      </c>
       <c r="C163">
         <v>1</v>
       </c>
@@ -15883,8 +16747,8 @@
       <c r="Y163" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA163" t="s">
-        <v>22</v>
+      <c r="Z163" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB163" t="s">
         <v>22</v>
@@ -15892,14 +16756,14 @@
       <c r="AC163" t="s">
         <v>22</v>
       </c>
-      <c r="AE163" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF163" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG163" s="5" t="s">
-        <v>21</v>
+      <c r="AD163" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF163" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG163" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH163" s="5" t="s">
         <v>21</v>
@@ -15907,11 +16771,17 @@
       <c r="AI163" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ163" s="9" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="164" spans="1:37">
+      <c r="AJ163" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK163" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="164" spans="1:38">
+      <c r="B164" s="1">
+        <v>15</v>
+      </c>
       <c r="C164">
         <v>2</v>
       </c>
@@ -15972,8 +16842,8 @@
       <c r="Y164" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA164" t="s">
-        <v>22</v>
+      <c r="Z164" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB164" t="s">
         <v>22</v>
@@ -15981,14 +16851,14 @@
       <c r="AC164" t="s">
         <v>22</v>
       </c>
-      <c r="AE164" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF164" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG164" s="5" t="s">
-        <v>21</v>
+      <c r="AD164" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF164" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG164" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH164" s="5" t="s">
         <v>21</v>
@@ -15996,11 +16866,17 @@
       <c r="AI164" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ164" s="1" t="s">
+      <c r="AJ164" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK164" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="165" spans="1:37">
+    <row r="165" spans="1:38">
+      <c r="B165" s="1">
+        <v>15</v>
+      </c>
       <c r="C165">
         <v>3</v>
       </c>
@@ -16061,8 +16937,8 @@
       <c r="Y165" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA165" t="s">
-        <v>22</v>
+      <c r="Z165" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB165" t="s">
         <v>22</v>
@@ -16070,8 +16946,8 @@
       <c r="AC165" t="s">
         <v>22</v>
       </c>
-      <c r="AE165" s="5" t="s">
-        <v>21</v>
+      <c r="AD165" t="s">
+        <v>22</v>
       </c>
       <c r="AF165" s="5" t="s">
         <v>21</v>
@@ -16085,11 +16961,17 @@
       <c r="AI165" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ165" t="s">
+      <c r="AJ165" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK165" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:37">
+    <row r="166" spans="1:38">
+      <c r="B166" s="1">
+        <v>15</v>
+      </c>
       <c r="C166">
         <v>4</v>
       </c>
@@ -16150,8 +17032,8 @@
       <c r="Y166" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA166" t="s">
-        <v>22</v>
+      <c r="Z166" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB166" t="s">
         <v>22</v>
@@ -16159,26 +17041,32 @@
       <c r="AC166" t="s">
         <v>22</v>
       </c>
-      <c r="AE166" s="5" t="s">
-        <v>21</v>
+      <c r="AD166" t="s">
+        <v>22</v>
       </c>
       <c r="AF166" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG166" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH166" s="5" t="s">
-        <v>21</v>
+      <c r="AG166" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH166" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI166" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ166" s="10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="167" spans="1:37">
+      <c r="AJ166" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK166" s="10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="167" spans="1:38">
+      <c r="B167" s="1">
+        <v>15</v>
+      </c>
       <c r="C167">
         <v>5</v>
       </c>
@@ -16239,8 +17127,8 @@
       <c r="Y167" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA167" t="s">
-        <v>22</v>
+      <c r="Z167" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB167" t="s">
         <v>22</v>
@@ -16248,26 +17136,32 @@
       <c r="AC167" t="s">
         <v>22</v>
       </c>
-      <c r="AE167" s="5" t="s">
-        <v>21</v>
+      <c r="AD167" t="s">
+        <v>22</v>
       </c>
       <c r="AF167" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG167" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH167" s="5" t="s">
-        <v>21</v>
+      <c r="AG167" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH167" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI167" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ167" s="1" t="s">
+      <c r="AJ167" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK167" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="168" spans="1:37">
+    <row r="168" spans="1:38">
+      <c r="B168" s="1">
+        <v>15</v>
+      </c>
       <c r="C168">
         <v>6</v>
       </c>
@@ -16328,8 +17222,8 @@
       <c r="Y168" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA168" t="s">
-        <v>22</v>
+      <c r="Z168" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB168" t="s">
         <v>22</v>
@@ -16337,8 +17231,8 @@
       <c r="AC168" t="s">
         <v>22</v>
       </c>
-      <c r="AE168" s="5" t="s">
-        <v>21</v>
+      <c r="AD168" t="s">
+        <v>22</v>
       </c>
       <c r="AF168" s="5" t="s">
         <v>21</v>
@@ -16352,14 +17246,17 @@
       <c r="AI168" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ168" t="s">
+      <c r="AJ168" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK168" t="s">
         <v>45</v>
       </c>
-      <c r="AK168" t="s">
+      <c r="AL168" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:37">
+    <row r="170" spans="1:38">
       <c r="A170" s="1" t="s">
         <v>149</v>
       </c>
@@ -16426,8 +17323,8 @@
       <c r="Y170" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA170" t="s">
-        <v>22</v>
+      <c r="Z170" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB170" t="s">
         <v>22</v>
@@ -16435,8 +17332,8 @@
       <c r="AC170" t="s">
         <v>22</v>
       </c>
-      <c r="AE170" s="5" t="s">
-        <v>21</v>
+      <c r="AD170" t="s">
+        <v>22</v>
       </c>
       <c r="AF170" s="5" t="s">
         <v>21</v>
@@ -16450,14 +17347,20 @@
       <c r="AI170" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ170" t="s">
+      <c r="AJ170" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK170" t="s">
         <v>55</v>
       </c>
-      <c r="AK170" t="s">
+      <c r="AL170" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="171" spans="1:37">
+    <row r="171" spans="1:38">
+      <c r="B171" s="1">
+        <v>16</v>
+      </c>
       <c r="C171">
         <v>1</v>
       </c>
@@ -16518,8 +17421,8 @@
       <c r="Y171" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA171" s="7" t="s">
-        <v>64</v>
+      <c r="Z171" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB171" s="7" t="s">
         <v>64</v>
@@ -16527,14 +17430,14 @@
       <c r="AC171" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE171" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF171" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG171" s="5" t="s">
-        <v>21</v>
+      <c r="AD171" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF171" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG171" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH171" s="5" t="s">
         <v>21</v>
@@ -16542,11 +17445,17 @@
       <c r="AI171" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ171" s="10" t="s">
+      <c r="AJ171" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK171" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="172" spans="1:37">
+    <row r="172" spans="1:38">
+      <c r="B172" s="1">
+        <v>16</v>
+      </c>
       <c r="C172">
         <v>2</v>
       </c>
@@ -16607,8 +17516,8 @@
       <c r="Y172" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA172" s="7" t="s">
-        <v>64</v>
+      <c r="Z172" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB172" s="7" t="s">
         <v>64</v>
@@ -16616,14 +17525,14 @@
       <c r="AC172" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE172" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF172" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG172" s="5" t="s">
-        <v>21</v>
+      <c r="AD172" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF172" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG172" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AH172" s="5" t="s">
         <v>21</v>
@@ -16631,11 +17540,17 @@
       <c r="AI172" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ172" s="1" t="s">
+      <c r="AJ172" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK172" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="173" spans="1:37">
+    <row r="173" spans="1:38">
+      <c r="B173" s="1">
+        <v>16</v>
+      </c>
       <c r="C173">
         <v>3</v>
       </c>
@@ -16696,8 +17611,8 @@
       <c r="Y173" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA173" s="7" t="s">
-        <v>64</v>
+      <c r="Z173" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB173" s="7" t="s">
         <v>64</v>
@@ -16705,8 +17620,8 @@
       <c r="AC173" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE173" s="5" t="s">
-        <v>21</v>
+      <c r="AD173" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF173" s="5" t="s">
         <v>21</v>
@@ -16720,11 +17635,17 @@
       <c r="AI173" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ173" t="s">
+      <c r="AJ173" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK173" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:37">
+    <row r="174" spans="1:38">
+      <c r="B174" s="1">
+        <v>16</v>
+      </c>
       <c r="C174">
         <v>4</v>
       </c>
@@ -16785,8 +17706,8 @@
       <c r="Y174" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA174" s="7" t="s">
-        <v>64</v>
+      <c r="Z174" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB174" s="7" t="s">
         <v>64</v>
@@ -16794,26 +17715,32 @@
       <c r="AC174" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE174" s="5" t="s">
-        <v>21</v>
+      <c r="AD174" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF174" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG174" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH174" s="5" t="s">
-        <v>21</v>
+      <c r="AG174" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH174" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI174" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ174" s="10" t="s">
+      <c r="AJ174" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK174" s="10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="175" spans="1:37">
+    <row r="175" spans="1:38">
+      <c r="B175" s="1">
+        <v>16</v>
+      </c>
       <c r="C175">
         <v>5</v>
       </c>
@@ -16874,8 +17801,8 @@
       <c r="Y175" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AA175" s="7" t="s">
-        <v>64</v>
+      <c r="Z175" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB175" s="7" t="s">
         <v>64</v>
@@ -16883,26 +17810,32 @@
       <c r="AC175" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE175" s="5" t="s">
-        <v>21</v>
+      <c r="AD175" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF175" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AG175" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH175" s="5" t="s">
-        <v>21</v>
+      <c r="AG175" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH175" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="AI175" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ175" s="1" t="s">
+      <c r="AJ175" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK175" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="176" spans="1:37">
+    <row r="176" spans="1:38">
+      <c r="B176" s="1">
+        <v>16</v>
+      </c>
       <c r="C176">
         <v>6</v>
       </c>
@@ -16963,8 +17896,8 @@
       <c r="Y176" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA176" s="7" t="s">
-        <v>64</v>
+      <c r="Z176" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="AB176" s="7" t="s">
         <v>64</v>
@@ -16972,8 +17905,8 @@
       <c r="AC176" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="AE176" s="5" t="s">
-        <v>21</v>
+      <c r="AD176" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="AF176" s="5" t="s">
         <v>21</v>
@@ -16987,10 +17920,13 @@
       <c r="AI176" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AJ176" t="s">
+      <c r="AJ176" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK176" t="s">
         <v>45</v>
       </c>
-      <c r="AK176" t="s">
+      <c r="AL176" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17012,200 +17948,200 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" t="s">
         <v>237</v>
-      </c>
-      <c r="B7" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" t="s">
         <v>238</v>
-      </c>
-      <c r="B8" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" t="s">
         <v>265</v>
-      </c>
-      <c r="B29" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -17213,7 +18149,7 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -17221,7 +18157,7 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -17229,7 +18165,7 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -17237,7 +18173,7 @@
         <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -17245,7 +18181,7 @@
         <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -17253,7 +18189,7 @@
         <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -17261,7 +18197,7 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -17269,7 +18205,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -17277,7 +18213,7 @@
         <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -17285,7 +18221,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -17293,7 +18229,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -17301,7 +18237,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -17309,7 +18245,7 @@
         <v>74</v>
       </c>
       <c r="B49" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -17317,7 +18253,7 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -17325,7 +18261,7 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -17333,7 +18269,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -17341,7 +18277,7 @@
         <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -17349,7 +18285,7 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -17357,7 +18293,7 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -17365,7 +18301,7 @@
         <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -17373,7 +18309,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -17381,12 +18317,12 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="B61" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -17394,7 +18330,7 @@
         <v>173</v>
       </c>
       <c r="B62" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -17402,7 +18338,7 @@
         <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -17410,7 +18346,7 @@
         <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -17418,15 +18354,15 @@
         <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B66" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/CPU Design/L1IsSequences.xlsx
+++ b/CPU Design/L1IsSequences.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Original" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'+Address bus'!$A$1:$AL$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'+Address bus'!$J$1:$J$176</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -9962,7 +9962,7 @@
         <v>8</v>
       </c>
       <c r="C87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>21</v>
@@ -10057,7 +10057,7 @@
         <v>8</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>21</v>
@@ -10155,7 +10155,7 @@
         <v>8</v>
       </c>
       <c r="C89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>21</v>
@@ -10253,7 +10253,7 @@
         <v>8</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>21</v>
@@ -10348,7 +10348,7 @@
         <v>8</v>
       </c>
       <c r="C91">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>21</v>
@@ -10446,7 +10446,7 @@
         <v>8</v>
       </c>
       <c r="C92">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>21</v>
@@ -10544,7 +10544,7 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>21</v>
@@ -10639,7 +10639,7 @@
         <v>8</v>
       </c>
       <c r="C94">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>21</v>
@@ -10737,7 +10737,7 @@
         <v>8</v>
       </c>
       <c r="C95">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>21</v>
@@ -10835,7 +10835,7 @@
         <v>8</v>
       </c>
       <c r="C96">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>21</v>
@@ -10933,7 +10933,7 @@
         <v>8</v>
       </c>
       <c r="C97">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>21</v>
@@ -11031,7 +11031,7 @@
         <v>8</v>
       </c>
       <c r="C98">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>21</v>
@@ -11129,7 +11129,7 @@
         <v>8</v>
       </c>
       <c r="C99">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>21</v>
@@ -11227,7 +11227,7 @@
         <v>8</v>
       </c>
       <c r="C100">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>21</v>
@@ -11325,7 +11325,7 @@
         <v>8</v>
       </c>
       <c r="C101">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>21</v>
@@ -11423,7 +11423,7 @@
         <v>8</v>
       </c>
       <c r="C102">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>24</v>
